--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 01:37:33</t>
+          <t>2026-06-30 03:44:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 03:44:12</t>
+          <t>2026-06-30 05:51:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 05:51:04</t>
+          <t>2026-06-30 07:57:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 07:57:45</t>
+          <t>2026-06-30 10:04:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 10:04:55</t>
+          <t>2026-06-30 12:11:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,254 +833,1270 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Estonian Premier League</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kuressaare</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Tallinna FC Flora</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K2" t="n">
+        <v>950</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:19:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Lyn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Asane</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:19:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Thor</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>KR Reykjavik</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>13</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X4" t="n">
+        <v>120</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>240</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:19:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>KA Akureyri</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:19:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Cuiaba</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>America MG</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.05</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q6" t="n">
         <v>1.01</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-30 12:11:53</t>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-30 14:19:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,7 +866,7 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="J2" t="n">
         <v>3.55</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.15</v>
@@ -905,7 +905,7 @@
         <v>1.48</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W2" t="n">
         <v>1.15</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
         <v>4.9</v>
@@ -1150,28 +1150,28 @@
         <v>1.64</v>
       </c>
       <c r="S3" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U3" t="n">
         <v>2.48</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X3" t="n">
         <v>40</v>
       </c>
       <c r="Y3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Z3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA3" t="n">
         <v>100</v>
@@ -1180,55 +1180,55 @@
         <v>20</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK3" t="n">
         <v>25</v>
       </c>
-      <c r="AK3" t="n">
-        <v>21</v>
-      </c>
       <c r="AL3" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AM3" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AN3" t="n">
         <v>7.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP3" t="n">
         <v>19.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1252,7 +1252,7 @@
         <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BB3" t="n">
         <v>14.5</v>
@@ -1261,16 +1261,16 @@
         <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
         <v>5.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH3" t="n">
         <v>4.7</v>
@@ -1282,7 +1282,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,13 +1294,13 @@
         <v>5.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BP3" t="n">
         <v>12</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1312,7 +1312,7 @@
         <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1.41</v>
       </c>
       <c r="J4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K4" t="n">
         <v>7.8</v>
@@ -1398,13 +1398,13 @@
         <v>5.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="R4" t="n">
         <v>2.78</v>
       </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
         <v>1.38</v>
@@ -1413,7 +1413,7 @@
         <v>3.1</v>
       </c>
       <c r="V4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="W4" t="n">
         <v>1.13</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,43 +1610,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Ymir</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
         <v>1.07</v>
@@ -1655,448 +1655,702 @@
         <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 14:19:19</t>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>KA Akureyri</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:26:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Cuiaba</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>America MG</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>1.05</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-30 14:19:19</t>
+      <c r="Q7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-30 16:26:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="I2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -881,34 +881,34 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>5.1</v>
+        <v>1.47</v>
       </c>
       <c r="O2" t="n">
         <v>1.15</v>
       </c>
       <c r="P2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1.23</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.22</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="T2" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="U2" t="n">
         <v>1.48</v>
       </c>
       <c r="V2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 16:26:37</t>
+          <t>2026-06-30 18:33:41</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G3" t="n">
         <v>1.91</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 16:26:37</t>
+          <t>2026-06-30 18:33:41</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
         <v>2.78</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T4" t="n">
         <v>1.38</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 16:26:37</t>
+          <t>2026-06-30 18:33:41</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1646,19 +1646,19 @@
         <v>1.08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
         <v>1.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R5" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 16:26:37</t>
+          <t>2026-06-30 18:33:41</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
         <v>1.01</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="P6" t="n">
         <v>1.07</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 16:26:37</t>
+          <t>2026-06-30 18:33:41</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 16:26:37</t>
+          <t>2026-06-30 18:33:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -863,16 +863,16 @@
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="I2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.15</v>
@@ -893,10 +893,10 @@
         <v>1.23</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="T2" t="n">
         <v>1.27</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P7" t="n">
-        <v>1.05</v>
+        <v>1.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 18:33:41</t>
+          <t>2026-06-30 20:40:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,94 +857,94 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="H2" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="I2" t="n">
-        <v>1.82</v>
+        <v>1.38</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>1.31</v>
+        <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="S2" t="n">
-        <v>1.23</v>
+        <v>2.34</v>
       </c>
       <c r="T2" t="n">
-        <v>1.27</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -962,67 +962,67 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>2.78</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>2.76</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>2.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1055,16 +1055,16 @@
         <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 20:40:51</t>
+          <t>2026-06-30 22:48:17</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 20:40:51</t>
+          <t>2026-06-30 22:48:17</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
         <v>8.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I4" t="n">
         <v>1.41</v>
@@ -1380,7 +1380,7 @@
         <v>6.6</v>
       </c>
       <c r="K4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>1.11</v>
@@ -1401,10 +1401,10 @@
         <v>1.17</v>
       </c>
       <c r="R4" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T4" t="n">
         <v>1.38</v>
@@ -1452,7 +1452,7 @@
         <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ4" t="n">
         <v>240</v>
@@ -1470,13 +1470,13 @@
         <v>38</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
@@ -1485,7 +1485,7 @@
         <v>13.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU4" t="n">
         <v>17</v>
@@ -1497,10 +1497,10 @@
         <v>10.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AZ4" t="n">
         <v>14.5</v>
@@ -1509,19 +1509,19 @@
         <v>14.5</v>
       </c>
       <c r="BB4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.7</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BD4" t="n">
         <v>5.5</v>
       </c>
-      <c r="BD4" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BE4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG4" t="n">
         <v>2.44</v>
@@ -1545,7 +1545,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BO4" t="n">
         <v>6</v>
@@ -1563,7 +1563,7 @@
         <v>8</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU4" t="n">
         <v>4.3</v>
@@ -1575,27 +1575,27 @@
         <v>6</v>
       </c>
       <c r="BX4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BY4" t="n">
         <v>6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 20:40:51</t>
+          <t>2026-06-30 22:48:17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,27 +1605,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ymir</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1634,7 +1634,7 @@
         <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.08</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Q5" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="R5" t="n">
         <v>1.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 20:40:51</t>
+          <t>2026-06-30 22:48:17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,36 +1859,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R6" t="n">
         <v>1.08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -2089,268 +2089,2046 @@
         <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 20:40:51</t>
+          <t>2026-06-30 22:48:17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Olympique Dcheira</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Olympic Safi</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K7" t="n">
+        <v>950</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-30 22:48:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RSB Berkane</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Wydad Casablanca</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K8" t="n">
+        <v>950</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-30 22:48:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Union de Touarga</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>IRT Tanger</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K9" t="n">
+        <v>950</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-30 22:48:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Raja Casablanca</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>HUSA Agadir</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-30 22:48:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Kawkab Marrakech</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MAS Maghrib A Fes</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K11" t="n">
+        <v>950</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-30 22:48:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Icelandic 3 Deild</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ymir</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>KV Vesturbaejar</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-30 22:48:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>KA Akureyri</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-30 22:48:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Cuiaba</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>America MG</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F14" t="n">
         <v>1.85</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G14" t="n">
         <v>1.95</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H14" t="n">
         <v>5.3</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I14" t="n">
         <v>5.8</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J14" t="n">
         <v>3.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K14" t="n">
         <v>3.55</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L14" t="n">
         <v>1.47</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M14" t="n">
         <v>1.11</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N14" t="n">
         <v>2.72</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O14" t="n">
         <v>1.51</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P14" t="n">
         <v>1.58</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q14" t="n">
         <v>2.48</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R14" t="n">
         <v>1.21</v>
       </c>
-      <c r="S7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="S14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.2</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U14" t="n">
         <v>1.73</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V14" t="n">
         <v>1.2</v>
       </c>
-      <c r="W7" t="n">
+      <c r="W14" t="n">
         <v>2.04</v>
       </c>
-      <c r="X7" t="n">
+      <c r="X14" t="n">
         <v>11</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Y14" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="Z14" t="n">
         <v>44</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AA14" t="n">
         <v>200</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AB14" t="n">
         <v>6.8</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AC14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AD14" t="n">
         <v>24</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AE14" t="n">
         <v>120</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AF14" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AG14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AH14" t="n">
         <v>27</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AI14" t="n">
         <v>140</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AJ14" t="n">
         <v>23</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AK14" t="n">
         <v>27</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AL14" t="n">
         <v>60</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AM14" t="n">
         <v>240</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AN14" t="n">
         <v>22</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AO14" t="n">
         <v>210</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AP14" t="n">
         <v>8</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AQ14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AR14" t="n">
         <v>27</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AS14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AT14" t="n">
         <v>5.6</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AU14" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AV14" t="n">
         <v>19</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AW14" t="n">
         <v>8</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AX14" t="n">
         <v>8.6</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="AY14" t="n">
         <v>9.6</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="AZ14" t="n">
         <v>6.4</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BA14" t="n">
         <v>8</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BB14" t="n">
         <v>18.5</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BC14" t="n">
         <v>21</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BD14" t="n">
         <v>42</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BE14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BF14" t="n">
         <v>16</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BG14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BH14" t="n">
         <v>2.9</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BI14" t="n">
         <v>2.36</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BJ14" t="n">
         <v>12.5</v>
       </c>
-      <c r="BK7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN7" t="n">
+      <c r="BK14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN14" t="n">
         <v>4.4</v>
       </c>
-      <c r="BO7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP7" t="n">
+      <c r="BO14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP14" t="n">
         <v>15.5</v>
       </c>
-      <c r="BQ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR7" t="n">
+      <c r="BQ14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BR14" t="n">
         <v>40</v>
       </c>
-      <c r="BS7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT7" t="n">
+      <c r="BS14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT14" t="n">
         <v>9</v>
       </c>
-      <c r="BU7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV7" t="n">
+      <c r="BU14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BV14" t="n">
         <v>60</v>
       </c>
-      <c r="BW7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX7" t="n">
+      <c r="BW14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BX14" t="n">
         <v>80</v>
       </c>
-      <c r="BY7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ7" t="n">
+      <c r="BY14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ14" t="n">
         <v>40</v>
       </c>
-      <c r="CA7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-06-30 20:40:51</t>
+      <c r="CA14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-30 22:48:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -860,16 +860,16 @@
         <v>8.6</v>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="I2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="K2" t="n">
         <v>6.8</v>
@@ -890,28 +890,28 @@
         <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R2" t="n">
         <v>1.63</v>
       </c>
       <c r="S2" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V2" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="W2" t="n">
         <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y2" t="n">
         <v>970</v>
@@ -923,7 +923,7 @@
         <v>970</v>
       </c>
       <c r="AB2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AC2" t="n">
         <v>970</v>
@@ -935,10 +935,10 @@
         <v>970</v>
       </c>
       <c r="AF2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AG2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH2" t="n">
         <v>29</v>
@@ -953,10 +953,10 @@
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
@@ -965,58 +965,58 @@
         <v>5.1</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.78</v>
+        <v>3.55</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.86</v>
+        <v>3.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.86</v>
+        <v>3.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.76</v>
+        <v>3.55</v>
       </c>
       <c r="BA2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BD2" t="n">
         <v>2.8</v>
       </c>
-      <c r="BB2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BC2" t="n">
+      <c r="BE2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BG2" t="n">
         <v>3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.9</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
         <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>15.5</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
         <v>8.199999999999999</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -1368,19 +1368,19 @@
         <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="I4" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="J4" t="n">
         <v>6.6</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L4" t="n">
         <v>1.11</v>
@@ -1404,19 +1404,19 @@
         <v>2.84</v>
       </c>
       <c r="S4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
         <v>120</v>
@@ -1425,10 +1425,10 @@
         <v>38</v>
       </c>
       <c r="Z4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB4" t="n">
         <v>95</v>
@@ -1470,13 +1470,13 @@
         <v>38</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
@@ -1485,7 +1485,7 @@
         <v>13.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
         <v>17</v>
@@ -1497,10 +1497,10 @@
         <v>10.5</v>
       </c>
       <c r="AX4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY4" t="n">
         <v>5.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>5.3</v>
       </c>
       <c r="AZ4" t="n">
         <v>14.5</v>
@@ -1509,31 +1509,31 @@
         <v>14.5</v>
       </c>
       <c r="BB4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD4" t="n">
         <v>5.9</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BE4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF4" t="n">
         <v>5.7</v>
       </c>
-      <c r="BD4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BG4" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="BH4" t="n">
         <v>8.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
         <v>5.1</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN4" t="n">
         <v>14</v>
@@ -1563,19 +1563,19 @@
         <v>8</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW4" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BX4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BY4" t="n">
         <v>6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1649,7 +1649,7 @@
         <v>1.43</v>
       </c>
       <c r="P5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q5" t="n">
         <v>1.43</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1900,7 +1900,7 @@
         <v>1.09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="n">
         <v>1.08</v>
@@ -1921,10 +1921,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -2154,13 +2154,13 @@
         <v>1.09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R7" t="n">
         <v>1.08</v>
@@ -2175,10 +2175,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2408,10 +2408,10 @@
         <v>1.09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q8" t="n">
         <v>1.44</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2659,10 +2659,10 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P9" t="n">
         <v>1.08</v>
@@ -2683,10 +2683,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -2901,10 +2901,10 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,7 +2913,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O10" t="n">
         <v>1.4</v>
@@ -2928,7 +2928,7 @@
         <v>1.08</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2937,10 +2937,10 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
@@ -3170,19 +3170,19 @@
         <v>1.09</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
         <v>1.08</v>
       </c>
       <c r="S11" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3191,10 +3191,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
         <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4094,7 +4094,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="BR14" t="n">
         <v>40</v>
@@ -4106,7 +4106,7 @@
         <v>9</v>
       </c>
       <c r="BU14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV14" t="n">
         <v>60</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-30 22:48:17</t>
+          <t>2026-07-01 00:55:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -857,58 +857,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="J2" t="n">
         <v>5.2</v>
       </c>
       <c r="K2" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="Q2" t="n">
         <v>1.55</v>
       </c>
       <c r="R2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
         <v>29</v>
@@ -923,7 +923,7 @@
         <v>970</v>
       </c>
       <c r="AB2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AC2" t="n">
         <v>970</v>
@@ -935,13 +935,13 @@
         <v>970</v>
       </c>
       <c r="AF2" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AG2" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AH2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
         <v>36</v>
@@ -950,127 +950,127 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM2" t="n">
         <v>130</v>
       </c>
-      <c r="AM2" t="n">
-        <v>140</v>
-      </c>
       <c r="AN2" t="n">
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV2" t="n">
         <v>4</v>
       </c>
-      <c r="AS2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AW2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BA2" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.84</v>
+        <v>4.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BT2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -1126,7 +1126,7 @@
         <v>4.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.23</v>
@@ -1141,22 +1141,22 @@
         <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q3" t="n">
         <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T3" t="n">
         <v>1.55</v>
       </c>
       <c r="U3" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V3" t="n">
         <v>1.27</v>
@@ -1219,16 +1219,16 @@
         <v>34</v>
       </c>
       <c r="AP3" t="n">
-        <v>19.5</v>
+        <v>7.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1252,25 +1252,25 @@
         <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="BC3" t="n">
         <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH3" t="n">
         <v>4.7</v>
@@ -1279,7 +1279,7 @@
         <v>3.55</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK3" t="n">
         <v>5.6</v>
@@ -1288,13 +1288,13 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
         <v>5.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP3" t="n">
         <v>12</v>
@@ -1306,7 +1306,7 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT3" t="n">
         <v>8.4</v>
@@ -1318,13 +1318,13 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>1.32</v>
       </c>
       <c r="I4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="J4" t="n">
         <v>6.6</v>
@@ -1413,7 +1413,7 @@
         <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="W4" t="n">
         <v>1.12</v>
@@ -1476,7 +1476,7 @@
         <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
@@ -1485,7 +1485,7 @@
         <v>13.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU4" t="n">
         <v>17</v>
@@ -1500,7 +1500,7 @@
         <v>6.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AZ4" t="n">
         <v>14.5</v>
@@ -1512,7 +1512,7 @@
         <v>6.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
         <v>5.9</v>
@@ -1521,7 +1521,7 @@
         <v>5.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
         <v>2.36</v>
@@ -1530,7 +1530,7 @@
         <v>8.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.800000000000001</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
         <v>14</v>
@@ -1554,25 +1554,25 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>5.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BX4" t="n">
         <v>14</v>
@@ -1581,14 +1581,14 @@
         <v>6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="CA4" t="n">
         <v>4.1</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>1.04</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>1.04</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>1.04</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
         <v>1.04</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>1.04</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
         <v>1.04</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2919,7 +2919,7 @@
         <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q10" t="n">
         <v>1.4</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>1.04</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q11" t="n">
         <v>2.6</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>1.85</v>
       </c>
       <c r="G14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H14" t="n">
         <v>5.3</v>
@@ -3956,7 +3956,7 @@
         <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X14" t="n">
         <v>11</v>
@@ -4010,7 +4010,7 @@
         <v>22</v>
       </c>
       <c r="AO14" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP14" t="n">
         <v>8</v>
@@ -4076,7 +4076,7 @@
         <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4106,7 +4106,7 @@
         <v>9</v>
       </c>
       <c r="BU14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV14" t="n">
         <v>60</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-01 00:55:49</t>
+          <t>2026-07-01 03:03:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H2" t="n">
         <v>1.36</v>
       </c>
       <c r="I2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.24</v>
@@ -881,13 +881,13 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="Q2" t="n">
         <v>1.55</v>
@@ -902,13 +902,13 @@
         <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V2" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X2" t="n">
         <v>29</v>
@@ -938,7 +938,7 @@
         <v>100</v>
       </c>
       <c r="AG2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AH2" t="n">
         <v>27</v>
@@ -953,7 +953,7 @@
         <v>150</v>
       </c>
       <c r="AL2" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM2" t="n">
         <v>130</v>
@@ -962,64 +962,64 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.5</v>
+        <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.8</v>
+        <v>2.54</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.1</v>
+        <v>2.34</v>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.2</v>
+        <v>2.36</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.9</v>
+        <v>2.58</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.7</v>
+        <v>2.52</v>
       </c>
       <c r="BA2" t="n">
-        <v>5</v>
+        <v>2.58</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.1</v>
+        <v>2.76</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.5</v>
+        <v>2.72</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.5</v>
+        <v>2.72</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BH2" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI2" t="n">
         <v>3.4</v>
@@ -1028,31 +1028,31 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO2" t="n">
         <v>2.64</v>
       </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.47</v>
+        <v>2.68</v>
       </c>
       <c r="BT2" t="n">
         <v>4.1</v>
@@ -1070,7 +1070,7 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.41</v>
+        <v>2.78</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -1141,10 +1141,10 @@
         <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R3" t="n">
         <v>1.65</v>
@@ -1165,13 +1165,13 @@
         <v>2.1</v>
       </c>
       <c r="X3" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z3" t="n">
         <v>40</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>55</v>
       </c>
       <c r="AA3" t="n">
         <v>100</v>
@@ -1219,7 +1219,7 @@
         <v>34</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>7</v>
@@ -1228,7 +1228,7 @@
         <v>8</v>
       </c>
       <c r="AS3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1252,10 +1252,10 @@
         <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
         <v>12</v>
@@ -1264,13 +1264,13 @@
         <v>7.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF3" t="n">
         <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="n">
         <v>4.7</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
@@ -1395,7 +1395,7 @@
         <v>1.05</v>
       </c>
       <c r="P4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Q4" t="n">
         <v>1.17</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -1619,94 +1619,94 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>1.66</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.09</v>
+        <v>2.96</v>
       </c>
       <c r="O5" t="n">
         <v>1.43</v>
       </c>
       <c r="P5" t="n">
-        <v>1.09</v>
+        <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.43</v>
+        <v>2.14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>2.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
@@ -1724,7 +1724,7 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP5" t="n">
         <v>1.03</v>
@@ -1778,71 +1778,71 @@
         <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -1873,112 +1873,112 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09</v>
+        <v>2.52</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.08</v>
+        <v>1.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.52</v>
+        <v>2.32</v>
       </c>
       <c r="R6" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.52</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.74</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP6" t="n">
         <v>1.03</v>
@@ -2029,74 +2029,74 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG6" t="n">
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -2127,112 +2127,112 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>1.09</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="P7" t="n">
-        <v>1.09</v>
+        <v>1.51</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.46</v>
+        <v>2.38</v>
       </c>
       <c r="R7" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="n">
         <v>1.03</v>
@@ -2289,68 +2289,68 @@
         <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
         <v>1.02</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -2916,19 +2916,19 @@
         <v>1.09</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P10" t="n">
         <v>1.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R10" t="n">
         <v>1.08</v>
       </c>
       <c r="S10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -3143,160 +3143,160 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="J11" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>2.12</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="R11" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
         <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -3305,68 +3305,68 @@
         <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -3397,160 +3397,160 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="H12" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="P12" t="n">
-        <v>1.07</v>
+        <v>4.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="R12" t="n">
-        <v>1.08</v>
+        <v>2.52</v>
       </c>
       <c r="S12" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AP12" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
         <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -3562,65 +3562,65 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
         <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.47</v>
@@ -3944,7 +3944,7 @@
         <v>1.21</v>
       </c>
       <c r="S14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T14" t="n">
         <v>2.2</v>
@@ -3953,7 +3953,7 @@
         <v>1.73</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
         <v>2.06</v>
@@ -3971,7 +3971,7 @@
         <v>200</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC14" t="n">
         <v>8.199999999999999</v>
@@ -4022,7 +4022,7 @@
         <v>27</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT14" t="n">
         <v>5.6</v>
@@ -4034,7 +4034,7 @@
         <v>19</v>
       </c>
       <c r="AW14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX14" t="n">
         <v>8.6</v>
@@ -4043,10 +4043,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB14" t="n">
         <v>18.5</v>
@@ -4058,13 +4058,13 @@
         <v>42</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF14" t="n">
         <v>16</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH14" t="n">
         <v>2.9</v>
@@ -4076,7 +4076,7 @@
         <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4088,7 +4088,7 @@
         <v>4.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="BP14" t="n">
         <v>15.5</v>
@@ -4106,7 +4106,7 @@
         <v>9</v>
       </c>
       <c r="BU14" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BV14" t="n">
         <v>60</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-01 03:03:10</t>
+          <t>2026-07-01 05:11:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="G2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="H2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I2" t="n">
         <v>1.36</v>
       </c>
-      <c r="I2" t="n">
-        <v>1.45</v>
-      </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="K2" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.24</v>
@@ -881,49 +881,49 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="R2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Y2" t="n">
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AA2" t="n">
         <v>970</v>
       </c>
       <c r="AB2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AC2" t="n">
         <v>970</v>
@@ -935,91 +935,91 @@
         <v>970</v>
       </c>
       <c r="AF2" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AG2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI2" t="n">
         <v>38</v>
       </c>
-      <c r="AH2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>36</v>
-      </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
         <v>120</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>970</v>
+        <v>5.3</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.54</v>
+        <v>4.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.34</v>
+        <v>4</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.36</v>
+        <v>3.95</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.58</v>
+        <v>4.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.52</v>
+        <v>4.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.58</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.76</v>
+        <v>5.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.72</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.72</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.72</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.74</v>
+        <v>5.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
         <v>3.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G3" t="n">
         <v>1.91</v>
@@ -1147,7 +1147,7 @@
         <v>1.51</v>
       </c>
       <c r="R3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S3" t="n">
         <v>2.26</v>
@@ -1165,82 +1165,82 @@
         <v>2.1</v>
       </c>
       <c r="X3" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Y3" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Z3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AA3" t="n">
         <v>100</v>
       </c>
       <c r="AB3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AC3" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI3" t="n">
         <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AM3" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AO3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>8</v>
+        <v>3.95</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1252,25 +1252,25 @@
         <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BC3" t="n">
         <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.2</v>
+        <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="BF3" t="n">
         <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>3.9</v>
       </c>
       <c r="BH3" t="n">
         <v>4.7</v>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1300,7 +1300,7 @@
         <v>12</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1312,7 +1312,7 @@
         <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="G4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="I4" t="n">
         <v>1.39</v>
       </c>
       <c r="J4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
@@ -1401,7 +1401,7 @@
         <v>1.17</v>
       </c>
       <c r="R4" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="S4" t="n">
         <v>1.44</v>
@@ -1416,7 +1416,7 @@
         <v>3.55</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
         <v>120</v>
@@ -1431,64 +1431,64 @@
         <v>22</v>
       </c>
       <c r="AB4" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AC4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AD4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
         <v>17.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AG4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>270</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN4" t="n">
         <v>44</v>
       </c>
-      <c r="AH4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>240</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>38</v>
-      </c>
       <c r="AO4" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AV4" t="n">
         <v>10.5</v>
@@ -1497,31 +1497,31 @@
         <v>10.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
         <v>14.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BG4" t="n">
         <v>2.36</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1619,37 +1619,37 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="I5" t="n">
         <v>1.66</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
         <v>4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
         <v>2.14</v>
@@ -1658,13 +1658,13 @@
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
         <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
         <v>2.5</v>
@@ -1673,37 +1673,37 @@
         <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AA5" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AB5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF5" t="n">
         <v>80</v>
       </c>
       <c r="AG5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AH5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="n">
         <v>60</v>
@@ -1724,61 +1724,61 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>2.58</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.66</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="BH5" t="n">
         <v>3.25</v>
@@ -1790,59 +1790,59 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.76</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="BT5" t="n">
         <v>3.95</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.800000000000001</v>
+        <v>2.34</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>19</v>
+        <v>1.11</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>2.28</v>
       </c>
       <c r="G6" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.44</v>
@@ -1900,19 +1900,19 @@
         <v>2.52</v>
       </c>
       <c r="O6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P6" t="n">
         <v>1.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="R6" t="n">
         <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
         <v>1.98</v>
@@ -1921,10 +1921,10 @@
         <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="X6" t="n">
         <v>11.5</v>
@@ -1933,16 +1933,16 @@
         <v>14.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="n">
         <v>130</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
         <v>22</v>
@@ -1963,10 +1963,10 @@
         <v>110</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
         <v>70</v>
@@ -1981,122 +1981,122 @@
         <v>120</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>19.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH6" t="n">
         <v>2.98</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ6" t="n">
         <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.800000000000001</v>
+        <v>2.22</v>
       </c>
       <c r="BN6" t="n">
         <v>5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP6" t="n">
         <v>19</v>
       </c>
       <c r="BQ6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
         <v>42</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BT6" t="n">
         <v>7.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="BV6" t="n">
         <v>44</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BX6" t="n">
         <v>65</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BZ6" t="n">
         <v>44</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="G7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N7" t="n">
         <v>2.8</v>
       </c>
-      <c r="H7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O7" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S7" t="n">
-        <v>1.48</v>
+        <v>4.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="U7" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="X7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA7" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC7" t="n">
         <v>8.4</v>
       </c>
-      <c r="AC7" t="n">
-        <v>8</v>
-      </c>
       <c r="AD7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF7" t="n">
         <v>16.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AM7" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AN7" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AO7" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>8.4</v>
+        <v>4.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN7" t="n">
         <v>5.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="BP7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BR7" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BT7" t="n">
         <v>6.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="BV7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BX7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2417,7 +2417,7 @@
         <v>1.44</v>
       </c>
       <c r="R8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S8" t="n">
         <v>1.44</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2683,10 +2683,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -2895,13 +2895,13 @@
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2937,7 +2937,7 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="G11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H11" t="n">
         <v>2.06</v>
       </c>
       <c r="I11" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J11" t="n">
         <v>2.76</v>
@@ -3161,10 +3161,10 @@
         <v>3.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="M11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
         <v>2.12</v>
@@ -3173,13 +3173,13 @@
         <v>1.56</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S11" t="n">
         <v>4.8</v>
@@ -3191,182 +3191,182 @@
         <v>1.56</v>
       </c>
       <c r="V11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z11" t="n">
         <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB11" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF11" t="n">
         <v>40</v>
       </c>
-      <c r="AF11" t="n">
-        <v>46</v>
-      </c>
       <c r="AG11" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AH11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI11" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ11" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AK11" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AL11" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AM11" t="n">
         <v>340</v>
       </c>
       <c r="AN11" t="n">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AO11" t="n">
         <v>38</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BJ11" t="n">
         <v>14.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BN11" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BT11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>5.2</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -3397,25 +3397,25 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="G12" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H12" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>1.09</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
@@ -3424,203 +3424,203 @@
         <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P12" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="R12" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="S12" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="T12" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="U12" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="Z12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AC12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD12" t="n">
         <v>21</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>22</v>
       </c>
       <c r="AE12" t="n">
         <v>32</v>
       </c>
       <c r="AF12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG12" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AI12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
         <v>23</v>
       </c>
       <c r="AM12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AN12" t="n">
-        <v>6.2</v>
+        <v>970</v>
       </c>
       <c r="AO12" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>
@@ -3908,10 +3908,10 @@
         <v>1.85</v>
       </c>
       <c r="G14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I14" t="n">
         <v>5.8</v>
@@ -3920,7 +3920,7 @@
         <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.47</v>
@@ -3938,13 +3938,13 @@
         <v>1.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R14" t="n">
         <v>1.21</v>
       </c>
       <c r="S14" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="T14" t="n">
         <v>2.2</v>
@@ -3956,10 +3956,10 @@
         <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y14" t="n">
         <v>14.5</v>
@@ -3971,10 +3971,10 @@
         <v>200</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
         <v>24</v>
@@ -4004,7 +4004,7 @@
         <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AN14" t="n">
         <v>22</v>
@@ -4019,22 +4019,22 @@
         <v>11.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT14" t="n">
         <v>5.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
         <v>19</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX14" t="n">
         <v>8.6</v>
@@ -4043,10 +4043,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB14" t="n">
         <v>18.5</v>
@@ -4055,16 +4055,16 @@
         <v>21</v>
       </c>
       <c r="BD14" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
         <v>16</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH14" t="n">
         <v>2.9</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-01 05:11:03</t>
+          <t>2026-07-01 07:18:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="I2" t="n">
         <v>1.36</v>
       </c>
       <c r="J2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K2" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.24</v>
@@ -881,43 +881,43 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>1.71</v>
       </c>
       <c r="O2" t="n">
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
         <v>1.64</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
         <v>3.75</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Y2" t="n">
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AA2" t="n">
         <v>970</v>
@@ -941,10 +941,10 @@
         <v>42</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -953,7 +953,7 @@
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AM2" t="n">
         <v>150</v>
@@ -965,61 +965,61 @@
         <v>5.3</v>
       </c>
       <c r="AP2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS2" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AT2" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="AX2" t="n">
-        <v>5</v>
+        <v>2.72</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.6</v>
+        <v>2.84</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.1</v>
+        <v>2.76</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>2.74</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>2.72</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>2.74</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.1</v>
+        <v>2.74</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BI2" t="n">
         <v>3.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
         <v>9</v>
       </c>
       <c r="AO3" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP3" t="n">
         <v>20</v>
@@ -1225,10 +1225,10 @@
         <v>17.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1252,7 +1252,7 @@
         <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB3" t="n">
         <v>14.5</v>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>1.31</v>
       </c>
       <c r="I4" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="J4" t="n">
         <v>6.8</v>
@@ -1413,7 +1413,7 @@
         <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="W4" t="n">
         <v>1.1</v>
@@ -1434,7 +1434,7 @@
         <v>100</v>
       </c>
       <c r="AC4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD4" t="n">
         <v>18</v>
@@ -1476,7 +1476,7 @@
         <v>5.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
@@ -1515,13 +1515,13 @@
         <v>5.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE4" t="n">
         <v>5.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG4" t="n">
         <v>2.36</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="H5" t="n">
         <v>1.51</v>
       </c>
       <c r="I5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="J5" t="n">
         <v>3.7</v>
@@ -1637,7 +1637,7 @@
         <v>4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
@@ -1649,25 +1649,25 @@
         <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
         <v>1.66</v>
       </c>
       <c r="V5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="W5" t="n">
         <v>1.12</v>
@@ -1697,7 +1697,7 @@
         <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AG5" t="n">
         <v>34</v>
@@ -1730,25 +1730,25 @@
         <v>5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AR5" t="n">
         <v>4.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.58</v>
+        <v>2.06</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AV5" t="n">
         <v>4.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.56</v>
+        <v>3.6</v>
       </c>
       <c r="AX5" t="n">
         <v>7.2</v>
@@ -1757,46 +1757,46 @@
         <v>6.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA5" t="n">
         <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.11</v>
+        <v>1.46</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
@@ -1808,41 +1808,41 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.7</v>
+        <v>2.72</v>
       </c>
       <c r="BT5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
         <v>2.94</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.44</v>
@@ -1906,13 +1906,13 @@
         <v>1.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="R6" t="n">
         <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T6" t="n">
         <v>1.98</v>
@@ -1924,7 +1924,7 @@
         <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="X6" t="n">
         <v>11.5</v>
@@ -1933,7 +1933,7 @@
         <v>14.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="n">
         <v>130</v>
@@ -1948,7 +1948,7 @@
         <v>22</v>
       </c>
       <c r="AE6" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF6" t="n">
         <v>15</v>
@@ -1963,10 +1963,10 @@
         <v>110</v>
       </c>
       <c r="AJ6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
         <v>70</v>
@@ -1981,64 +1981,64 @@
         <v>120</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AV6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ6" t="n">
+      <c r="BA6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB6" t="n">
         <v>4.3</v>
       </c>
-      <c r="BA6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BC6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE6" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE6" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BF6" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BH6" t="n">
         <v>2.98</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="BJ6" t="n">
         <v>12</v>
@@ -2056,7 +2056,7 @@
         <v>5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="BP6" t="n">
         <v>19</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G7" t="n">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="H7" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="J7" t="n">
         <v>2.94</v>
@@ -2145,118 +2145,118 @@
         <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="O7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="Q7" t="n">
         <v>2.22</v>
       </c>
       <c r="R7" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S7" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="U7" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="W7" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AA7" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AF7" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AK7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AN7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO7" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AP7" t="n">
         <v>3.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AU7" t="n">
         <v>3.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX7" t="n">
         <v>4</v>
@@ -2265,92 +2265,92 @@
         <v>3.9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC7" t="n">
         <v>4.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF7" t="n">
         <v>4.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.199999999999999</v>
+        <v>2.22</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR7" t="n">
         <v>42</v>
       </c>
       <c r="BS7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BV7" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>44</v>
+      </c>
+      <c r="CA7" t="n">
         <v>7.4</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>42</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>7</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
         <v>1.02</v>
       </c>
       <c r="P9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R9" t="n">
         <v>1.08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
@@ -2901,7 +2901,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -3143,31 +3143,31 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="G11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H11" t="n">
         <v>2.06</v>
       </c>
       <c r="I11" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="J11" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="M11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.56</v>
@@ -3176,7 +3176,7 @@
         <v>1.39</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R11" t="n">
         <v>1.13</v>
@@ -3191,7 +3191,7 @@
         <v>1.56</v>
       </c>
       <c r="V11" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="W11" t="n">
         <v>1.23</v>
@@ -3254,7 +3254,7 @@
         <v>3.35</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="AR11" t="n">
         <v>3.9</v>
@@ -3263,10 +3263,10 @@
         <v>4.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.7</v>
+        <v>3.35</v>
       </c>
       <c r="AV11" t="n">
         <v>3.95</v>
@@ -3275,7 +3275,7 @@
         <v>4.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY11" t="n">
         <v>4.5</v>
@@ -3284,22 +3284,22 @@
         <v>4.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG11" t="n">
         <v>4.8</v>
@@ -3308,7 +3308,7 @@
         <v>2.74</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="BJ11" t="n">
         <v>14.5</v>
@@ -3344,7 +3344,7 @@
         <v>5</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="BV11" t="n">
         <v>21</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -3427,13 +3427,13 @@
         <v>1.06</v>
       </c>
       <c r="P12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q12" t="n">
         <v>1.2</v>
       </c>
       <c r="R12" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
         <v>1.51</v>
@@ -3505,7 +3505,7 @@
         <v>970</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AQ12" t="n">
         <v>4.6</v>
@@ -3514,7 +3514,7 @@
         <v>4.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="AT12" t="n">
         <v>4.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>
@@ -3905,25 +3905,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G14" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H14" t="n">
         <v>5.2</v>
       </c>
       <c r="I14" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J14" t="n">
         <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
         <v>1.11</v>
@@ -3932,7 +3932,7 @@
         <v>2.72</v>
       </c>
       <c r="O14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P14" t="n">
         <v>1.58</v>
@@ -3947,7 +3947,7 @@
         <v>5.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U14" t="n">
         <v>1.73</v>
@@ -3956,7 +3956,7 @@
         <v>1.21</v>
       </c>
       <c r="W14" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X14" t="n">
         <v>9.800000000000001</v>
@@ -3974,7 +3974,7 @@
         <v>6.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
         <v>24</v>
@@ -4022,7 +4022,7 @@
         <v>26</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT14" t="n">
         <v>5.6</v>
@@ -4034,7 +4034,7 @@
         <v>19</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX14" t="n">
         <v>8.6</v>
@@ -4046,7 +4046,7 @@
         <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB14" t="n">
         <v>18.5</v>
@@ -4055,19 +4055,19 @@
         <v>21</v>
       </c>
       <c r="BD14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF14" t="n">
         <v>16</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH14" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BI14" t="n">
         <v>2.36</v>
@@ -4076,13 +4076,13 @@
         <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN14" t="n">
         <v>4.4</v>
@@ -4094,13 +4094,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR14" t="n">
         <v>40</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT14" t="n">
         <v>9</v>
@@ -4112,23 +4112,23 @@
         <v>60</v>
       </c>
       <c r="BW14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX14" t="n">
         <v>80</v>
       </c>
       <c r="BY14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ14" t="n">
         <v>40</v>
       </c>
       <c r="CA14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-01 07:18:53</t>
+          <t>2026-07-01 09:27:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -857,52 +857,52 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="I2" t="n">
         <v>1.36</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="K2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1.71</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="R2" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="T2" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
         <v>3.75</v>
@@ -911,7 +911,7 @@
         <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="Y2" t="n">
         <v>970</v>
@@ -923,7 +923,7 @@
         <v>970</v>
       </c>
       <c r="AB2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AC2" t="n">
         <v>970</v>
@@ -941,7 +941,7 @@
         <v>42</v>
       </c>
       <c r="AH2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI2" t="n">
         <v>36</v>
@@ -953,112 +953,112 @@
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AM2" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AR2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW2" t="n">
         <v>3.95</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AX2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>4.5</v>
       </c>
-      <c r="AT2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2.78</v>
-      </c>
       <c r="BA2" t="n">
-        <v>2.84</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.76</v>
+        <v>5.2</v>
       </c>
       <c r="BC2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG2" t="n">
         <v>2.74</v>
       </c>
-      <c r="BD2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3</v>
-      </c>
       <c r="BH2" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.54</v>
+        <v>6.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>2.64</v>
+        <v>1.61</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.68</v>
+        <v>1.51</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1070,7 +1070,7 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.78</v>
+        <v>1.54</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
@@ -1150,13 +1150,13 @@
         <v>1.64</v>
       </c>
       <c r="S3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V3" t="n">
         <v>1.27</v>
@@ -1180,7 +1180,7 @@
         <v>17</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD3" t="n">
         <v>22</v>
@@ -1189,7 +1189,7 @@
         <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG3" t="n">
         <v>13</v>
@@ -1213,46 +1213,46 @@
         <v>75</v>
       </c>
       <c r="AN3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AP3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17.5</v>
+        <v>3.65</v>
       </c>
       <c r="AR3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS3" t="n">
         <v>4</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.2</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>30</v>
+        <v>3.9</v>
       </c>
       <c r="AX3" t="n">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
         <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BB3" t="n">
         <v>14.5</v>
@@ -1261,16 +1261,16 @@
         <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>19</v>
+        <v>3.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF3" t="n">
         <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BH3" t="n">
         <v>4.7</v>
@@ -1294,7 +1294,7 @@
         <v>5.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="BP3" t="n">
         <v>12</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="I4" t="n">
         <v>1.34</v>
@@ -1416,7 +1416,7 @@
         <v>3.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
         <v>120</v>
@@ -1473,7 +1473,7 @@
         <v>2.68</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ4" t="n">
         <v>5.1</v>
@@ -1485,7 +1485,7 @@
         <v>13</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU4" t="n">
         <v>17.5</v>
@@ -1497,10 +1497,10 @@
         <v>10.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AZ4" t="n">
         <v>15.5</v>
@@ -1509,16 +1509,16 @@
         <v>14.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD4" t="n">
         <v>5.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF4" t="n">
         <v>5.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G5" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I5" t="n">
         <v>1.65</v>
@@ -1652,13 +1652,13 @@
         <v>1.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
         <v>2.2</v>
@@ -1676,7 +1676,7 @@
         <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="Z5" t="n">
         <v>970</v>
@@ -1688,7 +1688,7 @@
         <v>22</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
@@ -1703,7 +1703,7 @@
         <v>34</v>
       </c>
       <c r="AH5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
         <v>60</v>
@@ -1727,58 +1727,58 @@
         <v>970</v>
       </c>
       <c r="AP5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.06</v>
+        <v>5.4</v>
       </c>
       <c r="AU5" t="n">
         <v>4.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BH5" t="n">
         <v>3.3</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.04</v>
+        <v>1.59</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="H6" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="O6" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="W6" t="n">
-        <v>1.71</v>
+        <v>2.28</v>
       </c>
       <c r="X6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="Z6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD6" t="n">
         <v>36</v>
       </c>
-      <c r="AA6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>22</v>
-      </c>
       <c r="AE6" t="n">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="AF6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AI6" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AK6" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="AN6" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="AP6" t="n">
         <v>3.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AR6" t="n">
         <v>4.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AU6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AW6" t="n">
         <v>4.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AZ6" t="n">
         <v>4.1</v>
       </c>
       <c r="BA6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE6" t="n">
         <v>4.6</v>
       </c>
-      <c r="BB6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BF6" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="BG6" t="n">
         <v>4.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN6" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="BP6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BR6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BT6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>85</v>
+      </c>
+      <c r="BW6" t="n">
         <v>7.8</v>
       </c>
-      <c r="BU6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BX6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -2127,88 +2127,88 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="H7" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R7" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.79</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.69</v>
-      </c>
       <c r="X7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF7" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>15</v>
-      </c>
       <c r="AG7" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
         <v>25</v>
@@ -2217,52 +2217,52 @@
         <v>95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN7" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AO7" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU7" t="n">
         <v>3.3</v>
       </c>
-      <c r="AU7" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AV7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AW7" t="n">
         <v>5.1</v>
       </c>
       <c r="AX7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AZ7" t="n">
         <v>4.5</v>
@@ -2280,77 +2280,77 @@
         <v>5</v>
       </c>
       <c r="BE7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG7" t="n">
         <v>5.3</v>
       </c>
-      <c r="BF7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BH7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="BJ7" t="n">
         <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.22</v>
+        <v>8</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BP7" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.14</v>
+        <v>2.84</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
         <v>1.02</v>
       </c>
       <c r="P8" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="Q8" t="n">
         <v>1.44</v>
       </c>
       <c r="R8" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H9" t="n">
-        <v>1.15</v>
+        <v>2.2</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2659,7 +2659,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="O9" t="n">
         <v>1.02</v>
@@ -2668,13 +2668,13 @@
         <v>1.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2686,7 +2686,7 @@
         <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
@@ -2901,7 +2901,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2913,19 +2913,19 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.39</v>
       </c>
       <c r="P10" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
         <v>1.39</v>
       </c>
       <c r="R10" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
         <v>1.38</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="G11" t="n">
         <v>5.3</v>
@@ -3179,10 +3179,10 @@
         <v>2.62</v>
       </c>
       <c r="R11" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
         <v>2.2</v>
@@ -3197,7 +3197,7 @@
         <v>1.23</v>
       </c>
       <c r="X11" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="n">
         <v>7</v>
@@ -3254,34 +3254,34 @@
         <v>3.35</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AX11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA11" t="n">
         <v>9.199999999999999</v>
@@ -3302,7 +3302,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BH11" t="n">
         <v>2.74</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -3427,13 +3427,13 @@
         <v>1.06</v>
       </c>
       <c r="P12" t="n">
-        <v>4.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
         <v>1.2</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S12" t="n">
         <v>1.51</v>
@@ -3562,65 +3562,65 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
         <v>1.05</v>
       </c>
       <c r="P13" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
         <v>1.01</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G14" t="n">
         <v>1.92</v>
@@ -3920,7 +3920,7 @@
         <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.48</v>
@@ -3974,7 +3974,7 @@
         <v>6.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
         <v>24</v>
@@ -3989,13 +3989,13 @@
         <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
         <v>140</v>
       </c>
       <c r="AJ14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK14" t="n">
         <v>27</v>
@@ -4007,7 +4007,7 @@
         <v>250</v>
       </c>
       <c r="AN14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO14" t="n">
         <v>200</v>
@@ -4022,7 +4022,7 @@
         <v>26</v>
       </c>
       <c r="AS14" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AT14" t="n">
         <v>5.6</v>
@@ -4034,7 +4034,7 @@
         <v>19</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX14" t="n">
         <v>8.6</v>
@@ -4046,7 +4046,7 @@
         <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB14" t="n">
         <v>18.5</v>
@@ -4055,16 +4055,16 @@
         <v>21</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF14" t="n">
         <v>16</v>
       </c>
       <c r="BG14" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BH14" t="n">
         <v>2.88</v>
@@ -4076,7 +4076,7 @@
         <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4088,7 +4088,7 @@
         <v>4.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BP14" t="n">
         <v>15.5</v>
@@ -4106,7 +4106,7 @@
         <v>9</v>
       </c>
       <c r="BU14" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BV14" t="n">
         <v>60</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-01 09:27:12</t>
+          <t>2026-07-01 11:35:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="I2" t="n">
         <v>1.36</v>
@@ -872,37 +872,37 @@
         <v>5.7</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="R2" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="S2" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="V2" t="n">
         <v>3.75</v>
@@ -911,22 +911,22 @@
         <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AA2" t="n">
         <v>970</v>
       </c>
       <c r="AB2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AD2" t="n">
         <v>970</v>
@@ -956,121 +956,121 @@
         <v>120</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN2" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AO2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AP2" t="n">
         <v>5</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH2" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR2" t="n">
+      <c r="BI2" t="n">
         <v>3.7</v>
       </c>
-      <c r="AS2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
         <v>6.2</v>
       </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1.52</v>
-      </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.61</v>
+        <v>6.6</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.51</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.51</v>
+        <v>6</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.54</v>
+        <v>8</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.77</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -1123,7 +1123,7 @@
         <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
         <v>4.8</v>
@@ -1135,7 +1135,7 @@
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
@@ -1147,7 +1147,7 @@
         <v>1.51</v>
       </c>
       <c r="R3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
         <v>2.28</v>
@@ -1156,10 +1156,10 @@
         <v>1.56</v>
       </c>
       <c r="U3" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
         <v>2.1</v>
@@ -1180,16 +1180,16 @@
         <v>17</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG3" t="n">
         <v>13</v>
@@ -1219,40 +1219,40 @@
         <v>40</v>
       </c>
       <c r="AP3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.65</v>
+        <v>17.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
         <v>14.5</v>
@@ -1261,7 +1261,7 @@
         <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BE3" t="n">
         <v>4</v>
@@ -1270,10 +1270,10 @@
         <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI3" t="n">
         <v>3.55</v>
@@ -1282,31 +1282,31 @@
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
         <v>5.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BP3" t="n">
         <v>12</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT3" t="n">
         <v>8.4</v>
@@ -1318,13 +1318,13 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O4" t="n">
         <v>1.05</v>
@@ -1401,10 +1401,10 @@
         <v>1.17</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T4" t="n">
         <v>1.4</v>
@@ -1461,22 +1461,22 @@
         <v>100</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
@@ -1485,7 +1485,7 @@
         <v>13</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU4" t="n">
         <v>17.5</v>
@@ -1497,10 +1497,10 @@
         <v>10.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AZ4" t="n">
         <v>15.5</v>
@@ -1509,19 +1509,19 @@
         <v>14.5</v>
       </c>
       <c r="BB4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.8</v>
       </c>
-      <c r="BC4" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF4" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.2</v>
       </c>
       <c r="BG4" t="n">
         <v>2.36</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -1619,91 +1619,91 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="G5" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="I5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="J5" t="n">
         <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
         <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="T5" t="n">
         <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="V5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AB5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF5" t="n">
         <v>85</v>
       </c>
       <c r="AG5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AH5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
         <v>60</v>
@@ -1712,137 +1712,137 @@
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN5" t="n">
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.95</v>
+        <v>7.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX5" t="n">
         <v>5.4</v>
       </c>
-      <c r="AU5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AY5" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.89</v>
+        <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.06</v>
+        <v>5.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.06</v>
+        <v>5.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.89</v>
+        <v>5.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.89</v>
+        <v>5.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH5" t="n">
         <v>3.3</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO5" t="n">
         <v>5.6</v>
       </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.47</v>
+        <v>9.6</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>2.72</v>
+        <v>9.6</v>
       </c>
       <c r="BT5" t="n">
         <v>3.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.58</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.41</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -1873,61 +1873,61 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="G6" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="H6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O6" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W6" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="n">
         <v>21</v>
@@ -1936,167 +1936,167 @@
         <v>70</v>
       </c>
       <c r="AA6" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE6" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI6" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK6" t="n">
         <v>27</v>
       </c>
       <c r="AL6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN6" t="n">
         <v>18.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.8</v>
+        <v>15</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS6" t="n">
         <v>4.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.88</v>
+        <v>4.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AW6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BA6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.8</v>
+        <v>15</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.95</v>
+        <v>19</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
         <v>4.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.7</v>
+        <v>13</v>
       </c>
       <c r="BG6" t="n">
         <v>4.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="BJ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
         <v>13.5</v>
       </c>
-      <c r="BK6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BN6" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="BP6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BT6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BV6" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BZ6" t="n">
         <v>32</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="O7" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S7" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W7" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC7" t="n">
         <v>8.6</v>
       </c>
-      <c r="AC7" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG7" t="n">
         <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
         <v>30</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AR7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BB7" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BC7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>5</v>
+        <v>1.79</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.4</v>
+        <v>1.77</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.3</v>
+        <v>1.79</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="BP7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BX7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -2381,157 +2381,157 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>1.87</v>
       </c>
       <c r="H8" t="n">
-        <v>2.84</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>1.27</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.44</v>
+        <v>2.28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>1.45</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
         <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
         <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
         <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
         <v>1.03</v>
@@ -2543,10 +2543,10 @@
         <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
@@ -2561,7 +2561,7 @@
         <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -2635,160 +2635,160 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.45</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X9" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI9" t="n">
         <v>110</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2797,13 +2797,13 @@
         <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK9" t="n">
         <v>1.01</v>
@@ -2815,25 +2815,25 @@
         <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO9" t="n">
         <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ9" t="n">
         <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS9" t="n">
         <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU9" t="n">
         <v>1.01</v>
@@ -2851,14 +2851,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA9" t="n">
         <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -2889,118 +2889,118 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>1.6</v>
       </c>
       <c r="H10" t="n">
-        <v>1.11</v>
+        <v>6.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>2.96</v>
       </c>
       <c r="O10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.39</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>1.38</v>
+        <v>3.45</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>2.66</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
         <v>1.03</v>
@@ -3009,37 +3009,37 @@
         <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
         <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
         <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
         <v>1.03</v>
@@ -3051,13 +3051,13 @@
         <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK10" t="n">
         <v>1.01</v>
@@ -3069,25 +3069,25 @@
         <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BO10" t="n">
         <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ10" t="n">
         <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS10" t="n">
         <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU10" t="n">
         <v>1.01</v>
@@ -3105,14 +3105,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA10" t="n">
         <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="G11" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H11" t="n">
         <v>2.06</v>
       </c>
       <c r="I11" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="K11" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M11" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="P11" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="U11" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="V11" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="W11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>170</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>250</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV11" t="n">
         <v>9</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AW11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC11" t="n">
         <v>7</v>
       </c>
-      <c r="Z11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC11" t="n">
+      <c r="BD11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN11" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>130</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>340</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>230</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AS11" t="n">
+      <c r="BO11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT11" t="n">
         <v>4.6</v>
       </c>
-      <c r="AT11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>5</v>
-      </c>
       <c r="BU11" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="BV11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H12" t="n">
         <v>2.68</v>
@@ -3409,13 +3409,13 @@
         <v>3.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>100</v>
+        <v>10.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
@@ -3424,58 +3424,58 @@
         <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>4.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="R12" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="S12" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="T12" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="U12" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="V12" t="n">
         <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="Z12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AC12" t="n">
         <v>970</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE12" t="n">
         <v>32</v>
       </c>
       <c r="AF12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AG12" t="n">
         <v>970</v>
@@ -3487,37 +3487,37 @@
         <v>27</v>
       </c>
       <c r="AJ12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK12" t="n">
         <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AN12" t="n">
-        <v>970</v>
+        <v>6</v>
       </c>
       <c r="AO12" t="n">
         <v>970</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.9</v>
+        <v>2.32</v>
       </c>
       <c r="AQ12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT12" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4.5</v>
       </c>
       <c r="AU12" t="n">
         <v>4.1</v>
@@ -3532,10 +3532,10 @@
         <v>4.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BA12" t="n">
         <v>4.3</v>
@@ -3547,13 +3547,13 @@
         <v>4.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="BG12" t="n">
         <v>3.45</v>
@@ -3562,13 +3562,13 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3586,13 +3586,13 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G14" t="n">
         <v>1.92</v>
@@ -3917,10 +3917,10 @@
         <v>5.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
         <v>1.48</v>
@@ -4025,7 +4025,7 @@
         <v>8.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU14" t="n">
         <v>6.8</v>
@@ -4076,7 +4076,7 @@
         <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4088,7 +4088,7 @@
         <v>4.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="BP14" t="n">
         <v>15.5</v>
@@ -4106,7 +4106,7 @@
         <v>9</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="BV14" t="n">
         <v>60</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-01 11:35:30</t>
+          <t>2026-07-01 13:44:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="G2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="I2" t="n">
         <v>1.36</v>
       </c>
       <c r="J2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K2" t="n">
         <v>6.8</v>
@@ -881,28 +881,28 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S2" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T2" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
         <v>3.75</v>
@@ -911,28 +911,28 @@
         <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA2" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD2" t="n">
         <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AF2" t="n">
         <v>110</v>
@@ -944,97 +944,97 @@
         <v>30</v>
       </c>
       <c r="AI2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL2" t="n">
         <v>120</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AO2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC2" t="n">
         <v>5.3</v>
       </c>
-      <c r="AP2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS2" t="n">
+      <c r="BD2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG2" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>4.3</v>
       </c>
       <c r="BH2" t="n">
         <v>4.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BJ2" t="n">
         <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
@@ -1046,13 +1046,13 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6</v>
+        <v>2.64</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>6</v>
+        <v>2.64</v>
       </c>
       <c r="BT2" t="n">
         <v>4.1</v>
@@ -1064,13 +1064,13 @@
         <v>7.8</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
         <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.23</v>
@@ -1135,112 +1135,112 @@
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Y3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z3" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AA3" t="n">
         <v>100</v>
       </c>
       <c r="AB3" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH3" t="n">
         <v>19.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK3" t="n">
         <v>25</v>
       </c>
-      <c r="AK3" t="n">
-        <v>21</v>
-      </c>
       <c r="AL3" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
         <v>75</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AP3" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1252,37 +1252,37 @@
         <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.8</v>
+        <v>18.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.85</v>
+        <v>23</v>
       </c>
       <c r="BH3" t="n">
         <v>4.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BJ3" t="n">
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1303,7 +1303,7 @@
         <v>8.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS3" t="n">
         <v>7.8</v>
@@ -1312,7 +1312,7 @@
         <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>7.6</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="I4" t="n">
         <v>1.34</v>
       </c>
       <c r="J4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
         <v>8.199999999999999</v>
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.05</v>
       </c>
       <c r="P4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q4" t="n">
         <v>1.17</v>
       </c>
       <c r="R4" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="S4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T4" t="n">
         <v>1.4</v>
@@ -1425,7 +1425,7 @@
         <v>38</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
         <v>22</v>
@@ -1434,7 +1434,7 @@
         <v>100</v>
       </c>
       <c r="AC4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AD4" t="n">
         <v>18</v>
@@ -1461,7 +1461,7 @@
         <v>100</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
         <v>55</v>
@@ -1470,13 +1470,13 @@
         <v>42</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
@@ -1485,7 +1485,7 @@
         <v>13</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU4" t="n">
         <v>17.5</v>
@@ -1497,7 +1497,7 @@
         <v>10.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AY4" t="n">
         <v>5.4</v>
@@ -1509,10 +1509,10 @@
         <v>14.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD4" t="n">
         <v>5.5</v>
@@ -1521,13 +1521,13 @@
         <v>5.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI4" t="n">
         <v>4.8</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN4" t="n">
         <v>14</v>
@@ -1554,13 +1554,13 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
         <v>5.8</v>
@@ -1572,7 +1572,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BX4" t="n">
         <v>14</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>7.4</v>
       </c>
       <c r="G5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H5" t="n">
         <v>1.56</v>
@@ -1637,31 +1637,31 @@
         <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q5" t="n">
         <v>2.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U5" t="n">
         <v>1.69</v>
@@ -1673,148 +1673,148 @@
         <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AB5" t="n">
         <v>21</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AG5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
+        <v>190</v>
+      </c>
+      <c r="AL5" t="n">
         <v>180</v>
       </c>
-      <c r="AL5" t="n">
-        <v>170</v>
-      </c>
       <c r="AM5" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AN5" t="n">
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU5" t="n">
         <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY5" t="n">
         <v>23</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="BJ5" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN5" t="n">
         <v>12</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5" t="n">
         <v>3.9</v>
@@ -1826,7 +1826,7 @@
         <v>11</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1838,11 +1838,11 @@
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G6" t="n">
         <v>1.76</v>
@@ -1888,7 +1888,7 @@
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.42</v>
@@ -1897,25 +1897,25 @@
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
         <v>2.32</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
         <v>4.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
         <v>1.72</v>
@@ -1936,13 +1936,13 @@
         <v>70</v>
       </c>
       <c r="AA6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AB6" t="n">
         <v>6.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
         <v>34</v>
@@ -1963,13 +1963,13 @@
         <v>170</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
         <v>27</v>
       </c>
       <c r="AL6" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
         <v>270</v>
@@ -1978,19 +1978,19 @@
         <v>18.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AP6" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT6" t="n">
         <v>4.9</v>
@@ -1999,10 +1999,10 @@
         <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AX6" t="n">
         <v>7.8</v>
@@ -2011,34 +2011,34 @@
         <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH6" t="n">
         <v>2.96</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="BJ6" t="n">
         <v>12.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -2127,82 +2127,82 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="J7" t="n">
         <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.68</v>
+        <v>2.94</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="V7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W7" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA7" t="n">
         <v>140</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AC7" t="n">
         <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF7" t="n">
         <v>14</v>
@@ -2211,40 +2211,40 @@
         <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM7" t="n">
         <v>170</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
         <v>10.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.79</v>
+        <v>4.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.76</v>
+        <v>5.5</v>
       </c>
       <c r="AT7" t="n">
         <v>6</v>
@@ -2253,52 +2253,52 @@
         <v>5.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.79</v>
+        <v>5.3</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY7" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.75</v>
+        <v>5.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.79</v>
+        <v>5.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.77</v>
+        <v>5.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.79</v>
+        <v>5.4</v>
       </c>
       <c r="BH7" t="n">
         <v>3.05</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="BJ7" t="n">
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,7 +2310,7 @@
         <v>4.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BP7" t="n">
         <v>17</v>
@@ -2328,7 +2328,7 @@
         <v>7.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV7" t="n">
         <v>42</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G8" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="O8" t="n">
         <v>1.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R8" t="n">
         <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
         <v>1.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2441,19 +2441,19 @@
         <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE8" t="n">
         <v>130</v>
@@ -2465,10 +2465,10 @@
         <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
         <v>22</v>
@@ -2489,122 +2489,122 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BH8" t="n">
         <v>3.05</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN8" t="n">
         <v>4.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>2.06</v>
       </c>
       <c r="G9" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="H9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
         <v>4.7</v>
@@ -2653,28 +2653,28 @@
         <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="M9" t="n">
         <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.47</v>
       </c>
       <c r="P9" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="R9" t="n">
         <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
         <v>2.02</v>
@@ -2686,10 +2686,10 @@
         <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y9" t="n">
         <v>12.5</v>
@@ -2731,7 +2731,7 @@
         <v>28</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM9" t="n">
         <v>200</v>
@@ -2743,122 +2743,122 @@
         <v>120</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH9" t="n">
         <v>2.9</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BN9" t="n">
         <v>4.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP9" t="n">
         <v>17</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BR9" t="n">
         <v>38</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BT9" t="n">
         <v>7.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BZ9" t="n">
         <v>40</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G10" t="n">
         <v>1.6</v>
       </c>
       <c r="H10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
         <v>3.55</v>
@@ -2922,19 +2922,19 @@
         <v>1.71</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
         <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="T10" t="n">
         <v>2.26</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V10" t="n">
         <v>1.1</v>
@@ -2970,7 +2970,7 @@
         <v>9</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>36</v>
@@ -2997,58 +2997,58 @@
         <v>400</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH10" t="n">
         <v>3.25</v>
@@ -3060,59 +3060,59 @@
         <v>13.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BN10" t="n">
         <v>3.85</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP10" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BR10" t="n">
         <v>34</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT10" t="n">
         <v>12.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
         <v>25</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -3152,61 +3152,61 @@
         <v>2.06</v>
       </c>
       <c r="I11" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="J11" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="O11" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="P11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V11" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="W11" t="n">
         <v>1.24</v>
       </c>
       <c r="X11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AB11" t="n">
         <v>12</v>
@@ -3218,43 +3218,43 @@
         <v>12.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AF11" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AG11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH11" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AI11" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ11" t="n">
         <v>190</v>
       </c>
       <c r="AK11" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AL11" t="n">
         <v>170</v>
       </c>
       <c r="AM11" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AN11" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AO11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AR11" t="n">
         <v>9.4</v>
@@ -3263,55 +3263,55 @@
         <v>20</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="AY11" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BJ11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK11" t="n">
         <v>6.4</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN11" t="n">
         <v>8.4</v>
@@ -3332,41 +3332,41 @@
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT11" t="n">
         <v>4.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BV11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G12" t="n">
         <v>2.34</v>
@@ -3409,10 +3409,10 @@
         <v>3.5</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>1.09</v>
       </c>
       <c r="K12" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>1.12</v>
@@ -3433,10 +3433,10 @@
         <v>1.17</v>
       </c>
       <c r="R12" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="S12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T12" t="n">
         <v>1.23</v>
@@ -3454,22 +3454,22 @@
         <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
         <v>32</v>
@@ -3493,70 +3493,70 @@
         <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
         <v>32</v>
       </c>
       <c r="AN12" t="n">
-        <v>6</v>
+        <v>970</v>
       </c>
       <c r="AO12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.4</v>
+        <v>1.89</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.4</v>
+        <v>1.89</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.6</v>
+        <v>1.89</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.6</v>
+        <v>1.89</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.1</v>
+        <v>1.89</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.1</v>
+        <v>1.89</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.4</v>
+        <v>1.79</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.1</v>
+        <v>1.72</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.95</v>
+        <v>1.7</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.3</v>
+        <v>1.77</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.6</v>
+        <v>1.82</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.2</v>
+        <v>1.75</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.1</v>
+        <v>1.89</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.4</v>
+        <v>1.79</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.76</v>
+        <v>1.44</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.45</v>
+        <v>1.89</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3586,7 +3586,7 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2.16</v>
+        <v>4.5</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>
@@ -3917,10 +3917,10 @@
         <v>5.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.48</v>
@@ -3932,22 +3932,22 @@
         <v>2.72</v>
       </c>
       <c r="O14" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U14" t="n">
         <v>1.73</v>
@@ -3983,7 +3983,7 @@
         <v>120</v>
       </c>
       <c r="AF14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG14" t="n">
         <v>11.5</v>
@@ -4016,16 +4016,16 @@
         <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU14" t="n">
         <v>6.8</v>
@@ -4034,7 +4034,7 @@
         <v>19</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX14" t="n">
         <v>8.6</v>
@@ -4043,10 +4043,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>18.5</v>
@@ -4055,16 +4055,16 @@
         <v>21</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14" t="n">
         <v>16</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH14" t="n">
         <v>2.88</v>
@@ -4076,7 +4076,7 @@
         <v>12.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4088,13 +4088,13 @@
         <v>4.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BP14" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BR14" t="n">
         <v>40</v>
@@ -4106,7 +4106,7 @@
         <v>9</v>
       </c>
       <c r="BU14" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BV14" t="n">
         <v>60</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-01 13:44:07</t>
+          <t>2026-07-01 15:52:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,13 +872,13 @@
         <v>5.8</v>
       </c>
       <c r="K2" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
         <v>5.6</v>
@@ -893,7 +893,7 @@
         <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S2" t="n">
         <v>2.34</v>
@@ -902,7 +902,7 @@
         <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
         <v>3.75</v>
@@ -944,7 +944,7 @@
         <v>30</v>
       </c>
       <c r="AI2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -959,64 +959,64 @@
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AO2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX2" t="n">
         <v>5.4</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AY2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BA2" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD2" t="n">
         <v>5.4</v>
       </c>
-      <c r="BC2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BE2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH2" t="n">
         <v>4.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         <v>1.23</v>
       </c>
       <c r="M3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
         <v>5.6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
@@ -1395,22 +1395,22 @@
         <v>1.05</v>
       </c>
       <c r="P4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Q4" t="n">
         <v>1.17</v>
       </c>
       <c r="R4" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T4" t="n">
         <v>1.4</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V4" t="n">
         <v>3.9</v>
@@ -1530,7 +1530,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.800000000000001</v>
@@ -1542,19 +1542,19 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1563,7 +1563,7 @@
         <v>8</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU4" t="n">
         <v>4.3</v>
@@ -1575,20 +1575,20 @@
         <v>4.6</v>
       </c>
       <c r="BX4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BY4" t="n">
         <v>6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -1688,25 +1688,25 @@
         <v>21</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
         <v>80</v>
       </c>
       <c r="AG5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AH5" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
@@ -1718,13 +1718,13 @@
         <v>180</v>
       </c>
       <c r="AM5" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AN5" t="n">
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>970</v>
+        <v>240</v>
       </c>
       <c r="AP5" t="n">
         <v>8.4</v>
@@ -1745,16 +1745,16 @@
         <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
         <v>6.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AZ5" t="n">
         <v>6.8</v>
@@ -1772,7 +1772,7 @@
         <v>8.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF5" t="n">
         <v>8.6</v>
@@ -1790,7 +1790,7 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>9.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1820,7 +1820,7 @@
         <v>3.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BV5" t="n">
         <v>11</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -1864,239 +1864,239 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.67</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1.76</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9</v>
+        <v>1.09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.45</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>1.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.32</v>
+        <v>1.44</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="S6" t="n">
-        <v>4.6</v>
+        <v>1.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -2118,239 +2118,239 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="W7" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Z7" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AA7" t="n">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC7" t="n">
         <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AE7" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AF7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
         <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AJ7" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="AK7" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>170</v>
+        <v>270</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>110</v>
+        <v>290</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AS7" t="n">
         <v>5.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE7" t="n">
         <v>5.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BO7" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BP7" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="BQ7" t="n">
         <v>6.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BX7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BZ7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -2372,239 +2372,239 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.69</v>
+        <v>2.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="O8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="R8" t="n">
         <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="U8" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>30</v>
       </c>
-      <c r="AE8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>22</v>
-      </c>
       <c r="AK8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
         <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.15</v>
+        <v>6.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.15</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.15</v>
+        <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.2</v>
+        <v>18.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="BH8" t="n">
         <v>3.05</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -2626,214 +2626,214 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Union de Touarga</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IRT Tanger</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.06</v>
+        <v>1.69</v>
       </c>
       <c r="G9" t="n">
-        <v>2.24</v>
+        <v>1.79</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X9" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS9" t="n">
         <v>3.5</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AQ9" t="n">
+      <c r="AT9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
         <v>5.8</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AS9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>2.3</v>
-      </c>
       <c r="BT9" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
         <v>5.1</v>
@@ -2848,17 +2848,17 @@
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -2880,239 +2880,239 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HUSA Agadir</t>
+          <t>IRT Tanger</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.48</v>
+        <v>2.06</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6</v>
+        <v>2.24</v>
       </c>
       <c r="H10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV10" t="n">
         <v>6.8</v>
       </c>
-      <c r="I10" t="n">
+      <c r="AW10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>11</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X10" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>440</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="BK10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>17</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BZ10" t="n">
         <v>40</v>
       </c>
-      <c r="AE10" t="n">
-        <v>220</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>400</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>25</v>
-      </c>
       <c r="CA10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MAS Maghrib A Fes</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6</v>
+        <v>1.51</v>
       </c>
       <c r="G11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>440</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>220</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>390</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>5.1</v>
       </c>
-      <c r="H11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="AR11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>25</v>
+      </c>
+      <c r="CA11" t="n">
         <v>2.28</v>
       </c>
-      <c r="J11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>190</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>130</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>170</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>330</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>230</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>24</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>10.5</v>
-      </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ymir</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>MAS Maghrib A Fes</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.94</v>
+        <v>4.6</v>
       </c>
       <c r="G12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N12" t="n">
         <v>2.34</v>
       </c>
-      <c r="H12" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="O12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X12" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="L12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="Y12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>460</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>700</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>700</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>700</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BU12" t="n">
         <v>3.9</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.74</v>
+        <v>7.6</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.73</v>
+        <v>10</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,493 +3642,747 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Ymir</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O13" t="n">
         <v>1.05</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>4.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="R13" t="n">
-        <v>1.08</v>
+        <v>2.56</v>
       </c>
       <c r="S13" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-01 15:52:55</t>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>KA Akureyri</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="H14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I14" t="n">
+        <v>17</v>
+      </c>
+      <c r="J14" t="n">
+        <v>9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>44</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-07-01 18:02:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Cuiaba</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>America MG</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="F15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G15" t="n">
         <v>1.92</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H15" t="n">
         <v>5.2</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" t="n">
         <v>5.7</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>3.3</v>
       </c>
-      <c r="K14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="K15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L15" t="n">
         <v>1.48</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M15" t="n">
         <v>1.11</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N15" t="n">
         <v>2.72</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O15" t="n">
         <v>1.51</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P15" t="n">
         <v>1.57</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="Q15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.2</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S15" t="n">
         <v>5.2</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="T15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.73</v>
       </c>
-      <c r="V14" t="n">
+      <c r="V15" t="n">
         <v>1.21</v>
       </c>
-      <c r="W14" t="n">
+      <c r="W15" t="n">
         <v>2.08</v>
       </c>
-      <c r="X14" t="n">
+      <c r="X15" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Y15" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="Z15" t="n">
         <v>44</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA15" t="n">
         <v>200</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AB15" t="n">
         <v>6.8</v>
       </c>
-      <c r="AC14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AC15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD15" t="n">
         <v>24</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AE15" t="n">
         <v>120</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AF15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
         <v>11</v>
       </c>
-      <c r="AG14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL14" t="n">
+      <c r="BN15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BV15" t="n">
         <v>60</v>
       </c>
-      <c r="AM14" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY14" t="n">
+      <c r="BW15" t="n">
         <v>9.6</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BR14" t="n">
+      <c r="BX15" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>40</v>
       </c>
-      <c r="BS14" t="n">
+      <c r="CA15" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BT14" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>60</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>80</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>40</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>2026-07-01 15:52:55</t>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-07-01 18:02:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -863,7 +863,7 @@
         <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I2" t="n">
         <v>1.36</v>
@@ -872,7 +872,7 @@
         <v>5.8</v>
       </c>
       <c r="K2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.24</v>
@@ -881,28 +881,28 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S2" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
         <v>3.75</v>
@@ -911,115 +911,115 @@
         <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="Z2" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AB2" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AC2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AF2" t="n">
         <v>110</v>
       </c>
       <c r="AG2" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AI2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AK2" t="n">
         <v>160</v>
       </c>
       <c r="AL2" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AM2" t="n">
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV2" t="n">
         <v>9.4</v>
       </c>
-      <c r="AR2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AS2" t="n">
+      <c r="AW2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB2" t="n">
         <v>4.4</v>
       </c>
-      <c r="AT2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ2" t="n">
+      <c r="BC2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH2" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>4.6</v>
       </c>
       <c r="BI2" t="n">
         <v>4.1</v>
@@ -1028,7 +1028,7 @@
         <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1046,19 +1046,19 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BT2" t="n">
         <v>4.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV2" t="n">
         <v>7.8</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="H3" t="n">
         <v>4.1</v>
@@ -1123,10 +1123,10 @@
         <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.23</v>
@@ -1141,7 +1141,7 @@
         <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="Q3" t="n">
         <v>1.54</v>
@@ -1153,7 +1153,7 @@
         <v>2.32</v>
       </c>
       <c r="T3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U3" t="n">
         <v>2.48</v>
@@ -1162,7 +1162,7 @@
         <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="X3" t="n">
         <v>38</v>
@@ -1171,34 +1171,34 @@
         <v>28</v>
       </c>
       <c r="Z3" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AA3" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
         <v>19.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AF3" t="n">
         <v>17.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
         <v>19.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ3" t="n">
         <v>29</v>
@@ -1210,37 +1210,37 @@
         <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AO3" t="n">
         <v>48</v>
       </c>
       <c r="AP3" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1252,22 +1252,22 @@
         <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BD3" t="n">
         <v>18.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
         <v>23</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -1458,10 +1458,10 @@
         <v>270</v>
       </c>
       <c r="AK4" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM4" t="n">
         <v>55</v>
@@ -1473,10 +1473,10 @@
         <v>2.64</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
@@ -1485,7 +1485,7 @@
         <v>13</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU4" t="n">
         <v>17.5</v>
@@ -1497,7 +1497,7 @@
         <v>10.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY4" t="n">
         <v>5.4</v>
@@ -1509,10 +1509,10 @@
         <v>14.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BD4" t="n">
         <v>5.5</v>
@@ -1521,7 +1521,7 @@
         <v>5.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="BG4" t="n">
         <v>2.34</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="G5" t="n">
         <v>8.6</v>
@@ -1673,7 +1673,7 @@
         <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Y5" t="n">
         <v>7</v>
@@ -1682,25 +1682,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AB5" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AC5" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="AD5" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AE5" t="n">
         <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="AG5" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AH5" t="n">
         <v>500</v>
@@ -1724,10 +1724,10 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>240</v>
+        <v>28</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.7</v>
@@ -1736,19 +1736,19 @@
         <v>7</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.6</v>
+        <v>12</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
         <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX5" t="n">
         <v>8</v>
@@ -1763,22 +1763,22 @@
         <v>7.6</v>
       </c>
       <c r="BB5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC5" t="n">
         <v>8.6</v>
       </c>
-      <c r="BC5" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BD5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE5" t="n">
         <v>8.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH5" t="n">
         <v>3.25</v>
@@ -1820,7 +1820,7 @@
         <v>3.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BV5" t="n">
         <v>11</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,19 +1897,19 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R6" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
         <v>1.44</v>
@@ -1918,67 +1918,67 @@
         <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
         <v>1.03</v>
@@ -2026,13 +2026,13 @@
         <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="G7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H7" t="n">
         <v>6.4</v>
@@ -2142,7 +2142,7 @@
         <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
         <v>1.42</v>
@@ -2157,7 +2157,7 @@
         <v>1.45</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q7" t="n">
         <v>2.32</v>
@@ -2172,13 +2172,13 @@
         <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X7" t="n">
         <v>13</v>
@@ -2190,7 +2190,7 @@
         <v>70</v>
       </c>
       <c r="AA7" t="n">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
         <v>6.6</v>
@@ -2214,7 +2214,7 @@
         <v>34</v>
       </c>
       <c r="AI7" t="n">
-        <v>170</v>
+        <v>450</v>
       </c>
       <c r="AJ7" t="n">
         <v>18</v>
@@ -2223,16 +2223,16 @@
         <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM7" t="n">
-        <v>270</v>
+        <v>700</v>
       </c>
       <c r="AN7" t="n">
         <v>18.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>290</v>
+        <v>700</v>
       </c>
       <c r="AP7" t="n">
         <v>7.8</v>
@@ -2241,13 +2241,13 @@
         <v>12.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS7" t="n">
         <v>5.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AU7" t="n">
         <v>6.2</v>
@@ -2277,10 +2277,10 @@
         <v>15.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF7" t="n">
         <v>11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.04</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H8" t="n">
         <v>4.1</v>
@@ -2393,58 +2393,58 @@
         <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
         <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="O8" t="n">
         <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T8" t="n">
         <v>1.94</v>
       </c>
       <c r="U8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V8" t="n">
         <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA8" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
         <v>7.8</v>
@@ -2456,31 +2456,31 @@
         <v>19</v>
       </c>
       <c r="AE8" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AF8" t="n">
         <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
         <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AJ8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
         <v>23</v>
@@ -2495,10 +2495,10 @@
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AT8" t="n">
         <v>6.6</v>
@@ -2510,7 +2510,7 @@
         <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
@@ -2522,25 +2522,25 @@
         <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BE8" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BF8" t="n">
         <v>18.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH8" t="n">
         <v>3.05</v>
@@ -2582,7 +2582,7 @@
         <v>7.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV8" t="n">
         <v>42</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -2638,37 +2638,37 @@
         <v>1.69</v>
       </c>
       <c r="G9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.49</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O9" t="n">
         <v>1.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
@@ -2677,16 +2677,16 @@
         <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V9" t="n">
         <v>1.17</v>
       </c>
       <c r="W9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X9" t="n">
         <v>970</v>
@@ -2695,106 +2695,106 @@
         <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AD9" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AE9" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG9" t="n">
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ9" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>970</v>
+        <v>85</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV9" t="n">
         <v>3.05</v>
       </c>
-      <c r="AR9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AW9" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="AX9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BF9" t="n">
         <v>3.65</v>
       </c>
-      <c r="AY9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BG9" t="n">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="BH9" t="n">
         <v>3.05</v>
@@ -2818,7 +2818,7 @@
         <v>4.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
@@ -2848,17 +2848,17 @@
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.800000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G10" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
         <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
         <v>1.52</v>
@@ -2913,46 +2913,46 @@
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="O10" t="n">
         <v>1.47</v>
       </c>
       <c r="P10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q10" t="n">
         <v>2.38</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="T10" t="n">
         <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V10" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="X10" t="n">
         <v>10</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>7.6</v>
@@ -2961,7 +2961,7 @@
         <v>7.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
         <v>85</v>
@@ -2997,16 +2997,16 @@
         <v>120</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT10" t="n">
         <v>5.7</v>
@@ -3015,40 +3015,40 @@
         <v>5.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BA10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD10" t="n">
         <v>10</v>
       </c>
-      <c r="BB10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BE10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH10" t="n">
         <v>2.9</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>1.6</v>
       </c>
       <c r="H11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I11" t="n">
         <v>9.4</v>
@@ -3197,10 +3197,10 @@
         <v>2.66</v>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Z11" t="n">
         <v>90</v>
@@ -3215,28 +3215,28 @@
         <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AE11" t="n">
         <v>220</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI11" t="n">
         <v>200</v>
       </c>
       <c r="AJ11" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
@@ -3251,58 +3251,58 @@
         <v>390</v>
       </c>
       <c r="AP11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX11" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AY11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF11" t="n">
         <v>5.1</v>
       </c>
-      <c r="AR11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BH11" t="n">
         <v>3.25</v>
@@ -3326,13 +3326,13 @@
         <v>3.85</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="BP11" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="BR11" t="n">
         <v>34</v>
@@ -3344,7 +3344,7 @@
         <v>12.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -3418,10 +3418,10 @@
         <v>1.56</v>
       </c>
       <c r="M12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="O12" t="n">
         <v>1.59</v>
@@ -3445,13 +3445,13 @@
         <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W12" t="n">
         <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="n">
         <v>6.4</v>
@@ -3460,7 +3460,7 @@
         <v>11.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AB12" t="n">
         <v>12</v>
@@ -3472,19 +3472,19 @@
         <v>12.5</v>
       </c>
       <c r="AE12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF12" t="n">
         <v>38</v>
       </c>
-      <c r="AF12" t="n">
-        <v>42</v>
-      </c>
       <c r="AG12" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AH12" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AI12" t="n">
-        <v>460</v>
+        <v>200</v>
       </c>
       <c r="AJ12" t="n">
         <v>700</v>
@@ -3499,13 +3499,13 @@
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>700</v>
+        <v>230</v>
       </c>
       <c r="AO12" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ12" t="n">
         <v>5.3</v>
@@ -3514,7 +3514,7 @@
         <v>9.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
@@ -3523,52 +3523,52 @@
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AX12" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA12" t="n">
         <v>28</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BH12" t="n">
         <v>2.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="BJ12" t="n">
         <v>13</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,7 +3580,7 @@
         <v>8.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
@@ -3604,7 +3604,7 @@
         <v>18.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="G13" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="H13" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>3.2</v>
       </c>
       <c r="K13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>1.12</v>
@@ -3681,16 +3681,16 @@
         <v>1.05</v>
       </c>
       <c r="P13" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="R13" t="n">
         <v>2.56</v>
       </c>
       <c r="S13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T13" t="n">
         <v>1.23</v>
@@ -3699,37 +3699,37 @@
         <v>3.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y13" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="Z13" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AC13" t="n">
         <v>970</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AE13" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AG13" t="n">
         <v>970</v>
@@ -3738,76 +3738,76 @@
         <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AL13" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="AO13" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>2.5</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AR13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BA13" t="n">
-        <v>4.3</v>
+        <v>2.72</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.2</v>
+        <v>2.72</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.4</v>
+        <v>1.89</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="BG13" t="n">
         <v>3.45</v>
@@ -3822,59 +3822,59 @@
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
         <v>3.7</v>
       </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.5</v>
+        <v>1.63</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>2.2</v>
+        <v>1.49</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.73</v>
+        <v>1.19</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="O14" t="n">
         <v>1.08</v>
@@ -3944,7 +3944,7 @@
         <v>2.32</v>
       </c>
       <c r="S14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="T14" t="n">
         <v>1.79</v>
@@ -3959,7 +3959,7 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="Y14" t="n">
         <v>1000</v>
@@ -3977,7 +3977,7 @@
         <v>29</v>
       </c>
       <c r="AD14" t="n">
-        <v>65</v>
+        <v>230</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
@@ -3995,7 +3995,7 @@
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK14" t="n">
         <v>13.5</v>
@@ -4004,16 +4004,16 @@
         <v>36</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AQ14" t="n">
         <v>34</v>
@@ -4022,13 +4022,13 @@
         <v>46</v>
       </c>
       <c r="AS14" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AV14" t="n">
         <v>27</v>
@@ -4043,7 +4043,7 @@
         <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BA14" t="n">
         <v>40</v>
@@ -4055,7 +4055,7 @@
         <v>12</v>
       </c>
       <c r="BD14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BE14" t="n">
         <v>40</v>
@@ -4070,13 +4070,13 @@
         <v>6.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BJ14" t="n">
         <v>12</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
@@ -4094,7 +4094,7 @@
         <v>6.4</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BR14" t="n">
         <v>17</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G15" t="n">
         <v>1.92</v>
@@ -4174,7 +4174,7 @@
         <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L15" t="n">
         <v>1.48</v>
@@ -4183,13 +4183,13 @@
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O15" t="n">
         <v>1.51</v>
       </c>
       <c r="P15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q15" t="n">
         <v>2.54</v>
@@ -4261,7 +4261,7 @@
         <v>250</v>
       </c>
       <c r="AN15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
         <v>200</v>
@@ -4273,10 +4273,10 @@
         <v>12</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
         <v>5.6</v>
@@ -4288,7 +4288,7 @@
         <v>19</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX15" t="n">
         <v>8.6</v>
@@ -4309,16 +4309,16 @@
         <v>21</v>
       </c>
       <c r="BD15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
         <v>16</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH15" t="n">
         <v>2.88</v>
@@ -4348,7 +4348,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="BR15" t="n">
         <v>40</v>
@@ -4360,7 +4360,7 @@
         <v>9</v>
       </c>
       <c r="BU15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV15" t="n">
         <v>60</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-01 18:02:33</t>
+          <t>2026-07-01 20:12:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="G2" t="n">
         <v>11</v>
@@ -866,13 +866,13 @@
         <v>1.33</v>
       </c>
       <c r="I2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.24</v>
@@ -881,55 +881,55 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
         <v>1.66</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="T2" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y2" t="n">
         <v>21</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AB2" t="n">
         <v>100</v>
       </c>
       <c r="AC2" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>10.5</v>
+        <v>500</v>
       </c>
       <c r="AE2" t="n">
         <v>13.5</v>
@@ -941,7 +941,7 @@
         <v>95</v>
       </c>
       <c r="AH2" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
         <v>32</v>
@@ -965,16 +965,16 @@
         <v>4.6</v>
       </c>
       <c r="AP2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS2" t="n">
         <v>10</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
         <v>36</v>
@@ -989,31 +989,31 @@
         <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="AY2" t="n">
         <v>32</v>
       </c>
       <c r="AZ2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA2" t="n">
         <v>20</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG2" t="n">
         <v>4.1</v>
@@ -1037,25 +1037,25 @@
         <v>12.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO2" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.66</v>
+        <v>3.35</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BU2" t="n">
         <v>3.65</v>
@@ -1064,7 +1064,7 @@
         <v>7.8</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="G3" t="n">
         <v>1.86</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="G4" t="n">
         <v>9</v>
@@ -1380,7 +1380,7 @@
         <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>1.1</v>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="O4" t="n">
         <v>1.05</v>
@@ -1470,13 +1470,13 @@
         <v>42</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
@@ -1485,7 +1485,7 @@
         <v>13</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU4" t="n">
         <v>17.5</v>
@@ -1497,10 +1497,10 @@
         <v>10.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>15.5</v>
@@ -1509,16 +1509,16 @@
         <v>14.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF4" t="n">
         <v>10.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="I5" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
         <v>4.2</v>
@@ -1640,46 +1640,46 @@
         <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
         <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
         <v>2.22</v>
       </c>
       <c r="U5" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V5" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
         <v>19.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
         <v>44</v>
@@ -1691,10 +1691,10 @@
         <v>16</v>
       </c>
       <c r="AD5" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
         <v>400</v>
@@ -1712,10 +1712,10 @@
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AL5" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AM5" t="n">
         <v>700</v>
@@ -1727,22 +1727,22 @@
         <v>28</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AR5" t="n">
         <v>7</v>
       </c>
       <c r="AS5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
         <v>10.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV5" t="n">
         <v>6.2</v>
@@ -1751,34 +1751,34 @@
         <v>6.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH5" t="n">
         <v>3.25</v>
@@ -1790,7 +1790,7 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1814,13 +1814,13 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT5" t="n">
         <v>3.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BV5" t="n">
         <v>11</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="G6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD6" t="n">
         <v>19</v>
       </c>
-      <c r="H6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="I6" t="n">
-        <v>970</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>500</v>
-      </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AF6" t="n">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AK6" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AM6" t="n">
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.55</v>
+        <v>5.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -2127,67 +2127,67 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="H7" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="O7" t="n">
         <v>1.45</v>
       </c>
       <c r="P7" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
         <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U7" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W7" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Z7" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
@@ -2199,28 +2199,28 @@
         <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AE7" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI7" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="AJ7" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
         <v>120</v>
@@ -2229,128 +2229,128 @@
         <v>700</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO7" t="n">
         <v>700</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="AS7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT7" t="n">
         <v>5.5</v>
       </c>
-      <c r="AT7" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AU7" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.4</v>
+        <v>9.4</v>
       </c>
       <c r="AX7" t="n">
         <v>7.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BC7" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH7" t="n">
         <v>2.96</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="BJ7" t="n">
         <v>12.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BO7" t="n">
         <v>3.55</v>
       </c>
       <c r="BP7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>70</v>
+      </c>
+      <c r="BW7" t="n">
         <v>10</v>
       </c>
-      <c r="BT7" t="n">
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
         <v>10.5</v>
       </c>
-      <c r="BU7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>12</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -2387,10 +2387,10 @@
         <v>2.16</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
@@ -2411,19 +2411,19 @@
         <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q8" t="n">
         <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
         <v>4.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
         <v>1.88</v>
@@ -2438,10 +2438,10 @@
         <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
@@ -2456,7 +2456,7 @@
         <v>19</v>
       </c>
       <c r="AE8" t="n">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AF8" t="n">
         <v>14</v>
@@ -2471,7 +2471,7 @@
         <v>200</v>
       </c>
       <c r="AJ8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK8" t="n">
         <v>27</v>
@@ -2489,13 +2489,13 @@
         <v>110</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS8" t="n">
         <v>7.6</v>
@@ -2507,7 +2507,7 @@
         <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW8" t="n">
         <v>7.4</v>
@@ -2525,10 +2525,10 @@
         <v>7.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD8" t="n">
         <v>7</v>
@@ -2546,19 +2546,19 @@
         <v>3.05</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ8" t="n">
         <v>11.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN8" t="n">
         <v>4.8</v>
@@ -2570,41 +2570,41 @@
         <v>17</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR8" t="n">
         <v>38</v>
       </c>
       <c r="BS8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW8" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>42</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>8.6</v>
       </c>
       <c r="BX8" t="n">
         <v>60</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
         <v>38</v>
       </c>
       <c r="CA8" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -2638,19 +2638,19 @@
         <v>1.69</v>
       </c>
       <c r="G9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
         <v>1.49</v>
@@ -2659,10 +2659,10 @@
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P9" t="n">
         <v>1.66</v>
@@ -2677,16 +2677,16 @@
         <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W9" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X9" t="n">
         <v>970</v>
@@ -2701,7 +2701,7 @@
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="AC9" t="n">
         <v>15</v>
@@ -2725,7 +2725,7 @@
         <v>700</v>
       </c>
       <c r="AJ9" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
         <v>500</v>
@@ -2743,58 +2743,58 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR9" t="n">
         <v>2.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BD9" t="n">
         <v>2.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.65</v>
+        <v>6.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="BH9" t="n">
         <v>3.05</v>
@@ -2806,59 +2806,59 @@
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BN9" t="n">
         <v>4.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>2.3</v>
+        <v>7.2</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="G10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H10" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="I10" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
         <v>3.1</v>
@@ -2910,19 +2910,19 @@
         <v>1.52</v>
       </c>
       <c r="M10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="O10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R10" t="n">
         <v>1.23</v>
@@ -2931,58 +2931,58 @@
         <v>4.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y10" t="n">
         <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AA10" t="n">
-        <v>900</v>
+        <v>290</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC10" t="n">
         <v>7.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE10" t="n">
         <v>85</v>
       </c>
       <c r="AF10" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AJ10" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AK10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL10" t="n">
         <v>55</v>
@@ -2991,128 +2991,128 @@
         <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO10" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="AS10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX10" t="n">
         <v>11</v>
       </c>
-      <c r="AT10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW10" t="n">
+      <c r="AY10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE10" t="n">
         <v>10.5</v>
       </c>
-      <c r="AX10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD10" t="n">
+      <c r="BF10" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG10" t="n">
         <v>10</v>
       </c>
-      <c r="BE10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>11</v>
-      </c>
       <c r="BH10" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ10" t="n">
         <v>11</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.42</v>
+        <v>14.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>2.14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR10" t="n">
         <v>38</v>
       </c>
       <c r="BS10" t="n">
-        <v>2.3</v>
+        <v>11</v>
       </c>
       <c r="BT10" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW10" t="n">
-        <v>2.3</v>
+        <v>11</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.34</v>
+        <v>12</v>
       </c>
       <c r="BZ10" t="n">
         <v>40</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.3</v>
+        <v>11</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -3143,61 +3143,61 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="H11" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="R11" t="n">
         <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V11" t="n">
         <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y11" t="n">
         <v>23</v>
@@ -3215,7 +3215,7 @@
         <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AE11" t="n">
         <v>220</v>
@@ -3227,7 +3227,7 @@
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI11" t="n">
         <v>200</v>
@@ -3236,85 +3236,85 @@
         <v>14.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
         <v>280</v>
       </c>
       <c r="AN11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO11" t="n">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="AP11" t="n">
         <v>5.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="AR11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS11" t="n">
         <v>8.4</v>
       </c>
-      <c r="AS11" t="n">
-        <v>9</v>
-      </c>
       <c r="AT11" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="AU11" t="n">
         <v>5.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AW11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY11" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AX11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB11" t="n">
         <v>6.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BG11" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="BJ11" t="n">
         <v>13.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3326,16 +3326,16 @@
         <v>3.85</v>
       </c>
       <c r="BO11" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="BP11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS11" t="n">
         <v>8.199999999999999</v>
@@ -3344,7 +3344,7 @@
         <v>12.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3362,11 +3362,11 @@
         <v>25</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.28</v>
+        <v>7.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -3397,76 +3397,76 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="G12" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="H12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I12" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="J12" t="n">
         <v>2.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P12" t="n">
         <v>1.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="V12" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X12" t="n">
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AB12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>12.5</v>
@@ -3475,13 +3475,13 @@
         <v>46</v>
       </c>
       <c r="AF12" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AG12" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AH12" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AI12" t="n">
         <v>200</v>
@@ -3499,22 +3499,22 @@
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="AO12" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AP12" t="n">
         <v>6.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AR12" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
@@ -3541,31 +3541,31 @@
         <v>28</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="BJ12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BK12" t="n">
         <v>9.6</v>
@@ -3574,53 +3574,53 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BW12" t="n">
         <v>12</v>
       </c>
-      <c r="BN12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>13</v>
-      </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G13" t="n">
         <v>2.56</v>
@@ -3660,13 +3660,13 @@
         <v>2.42</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="K13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.12</v>
@@ -3675,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.02</v>
+        <v>12.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.05</v>
       </c>
       <c r="P13" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="R13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="S13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T13" t="n">
         <v>1.23</v>
@@ -3714,7 +3714,7 @@
         <v>500</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB13" t="n">
         <v>500</v>
@@ -3741,7 +3741,7 @@
         <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK13" t="n">
         <v>500</v>
@@ -3750,7 +3750,7 @@
         <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
         <v>55</v>
@@ -3759,55 +3759,55 @@
         <v>55</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.46</v>
+        <v>4.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.54</v>
+        <v>2.26</v>
       </c>
       <c r="AX13" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AY13" t="n">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.72</v>
+        <v>2.12</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.72</v>
+        <v>2.12</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.89</v>
+        <v>5.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BG13" t="n">
         <v>3.45</v>
@@ -3816,19 +3816,19 @@
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
@@ -3840,41 +3840,41 @@
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.19</v>
+        <v>1.61</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -3908,16 +3908,16 @@
         <v>1.2</v>
       </c>
       <c r="G14" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="H14" t="n">
         <v>14</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="K14" t="n">
         <v>10.5</v>
@@ -3938,16 +3938,16 @@
         <v>4.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
         <v>1.65</v>
       </c>
       <c r="T14" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U14" t="n">
         <v>2.14</v>
@@ -3968,7 +3968,7 @@
         <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>610</v>
       </c>
       <c r="AB14" t="n">
         <v>22</v>
@@ -3977,7 +3977,7 @@
         <v>29</v>
       </c>
       <c r="AD14" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
@@ -3986,28 +3986,28 @@
         <v>12.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH14" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AK14" t="n">
         <v>13.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AM14" t="n">
         <v>490</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
@@ -4022,7 +4022,7 @@
         <v>46</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="AT14" t="n">
         <v>17</v>
@@ -4049,19 +4049,19 @@
         <v>40</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE14" t="n">
         <v>40</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BG14" t="n">
         <v>44</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
         <v>2.74</v>
       </c>
       <c r="O15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P15" t="n">
         <v>1.58</v>
@@ -4198,7 +4198,7 @@
         <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T15" t="n">
         <v>2.2</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-01 20:12:01</t>
+          <t>2026-07-01 22:21:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -863,7 +863,7 @@
         <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="I2" t="n">
         <v>1.34</v>
@@ -872,7 +872,7 @@
         <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.24</v>
@@ -902,7 +902,7 @@
         <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
         <v>3.9</v>
@@ -911,13 +911,13 @@
         <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y2" t="n">
         <v>21</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>12.5</v>
@@ -929,7 +929,7 @@
         <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="AE2" t="n">
         <v>13.5</v>
@@ -941,7 +941,7 @@
         <v>95</v>
       </c>
       <c r="AH2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI2" t="n">
         <v>32</v>
@@ -956,7 +956,7 @@
         <v>260</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN2" t="n">
         <v>150</v>
@@ -965,7 +965,7 @@
         <v>4.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
         <v>9.4</v>
@@ -974,13 +974,13 @@
         <v>8</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
         <v>36</v>
       </c>
       <c r="AU2" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2" t="n">
         <v>9.4</v>
@@ -1004,19 +1004,19 @@
         <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.6</v>
+        <v>18</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.6</v>
+        <v>18.5</v>
       </c>
       <c r="BF2" t="n">
         <v>15</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH2" t="n">
         <v>4.7</v>
@@ -1028,13 +1028,13 @@
         <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>12.5</v>
+        <v>3.25</v>
       </c>
       <c r="BN2" t="n">
         <v>970</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="G3" t="n">
         <v>1.86</v>
@@ -1144,19 +1144,19 @@
         <v>2.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U3" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V3" t="n">
         <v>1.27</v>
@@ -1213,7 +1213,7 @@
         <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO3" t="n">
         <v>48</v>
@@ -1225,46 +1225,46 @@
         <v>15.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="AT3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY3" t="n">
         <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="BC3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD3" t="n">
         <v>18.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BF3" t="n">
         <v>6.6</v>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1300,7 +1300,7 @@
         <v>12</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
         <v>21</v>
@@ -1312,7 +1312,7 @@
         <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
         <v>9</v>
@@ -1395,22 +1395,22 @@
         <v>1.05</v>
       </c>
       <c r="P4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="S4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T4" t="n">
         <v>1.4</v>
       </c>
       <c r="U4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
         <v>3.9</v>
@@ -1461,22 +1461,22 @@
         <v>230</v>
       </c>
       <c r="AL4" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
         <v>55</v>
       </c>
       <c r="AN4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
@@ -1485,7 +1485,7 @@
         <v>13</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU4" t="n">
         <v>17.5</v>
@@ -1497,10 +1497,10 @@
         <v>10.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AZ4" t="n">
         <v>15.5</v>
@@ -1509,16 +1509,16 @@
         <v>14.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF4" t="n">
         <v>10.5</v>
@@ -1527,7 +1527,7 @@
         <v>2.34</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI4" t="n">
         <v>6.4</v>
@@ -1542,19 +1542,19 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN4" t="n">
         <v>14.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
@@ -1566,13 +1566,13 @@
         <v>5.9</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BX4" t="n">
         <v>13.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -1625,16 +1625,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="I5" t="n">
         <v>1.64</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.44</v>
@@ -1643,7 +1643,7 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.4</v>
@@ -1652,22 +1652,22 @@
         <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R5" t="n">
         <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T5" t="n">
         <v>2.22</v>
       </c>
       <c r="U5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V5" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="W5" t="n">
         <v>1.12</v>
@@ -1691,7 +1691,7 @@
         <v>16</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>9.6</v>
       </c>
       <c r="AE5" t="n">
         <v>65</v>
@@ -1724,22 +1724,22 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU5" t="n">
         <v>8</v>
@@ -1748,34 +1748,34 @@
         <v>6.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="BG5" t="n">
         <v>10</v>
@@ -1790,7 +1790,7 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="H6" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.47</v>
@@ -1897,13 +1897,13 @@
         <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O6" t="n">
         <v>1.47</v>
       </c>
       <c r="P6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q6" t="n">
         <v>2.26</v>
@@ -1912,19 +1912,19 @@
         <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
         <v>1.76</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="X6" t="n">
         <v>11</v>
@@ -1933,40 +1933,40 @@
         <v>13</v>
       </c>
       <c r="Z6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA6" t="n">
         <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC6" t="n">
         <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>160</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AJ6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
         <v>150</v>
@@ -1975,64 +1975,64 @@
         <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO6" t="n">
         <v>110</v>
       </c>
       <c r="AP6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AR6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV6" t="n">
         <v>5.2</v>
       </c>
-      <c r="AS6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AW6" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY6" t="n">
         <v>4.4</v>
       </c>
-      <c r="AY6" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH6" t="n">
         <v>2.94</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -2127,31 +2127,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="G7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="I7" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="M7" t="n">
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
         <v>1.45</v>
@@ -2160,7 +2160,7 @@
         <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R7" t="n">
         <v>1.22</v>
@@ -2172,22 +2172,22 @@
         <v>2.14</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X7" t="n">
         <v>11</v>
       </c>
       <c r="Y7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z7" t="n">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
@@ -2196,28 +2196,28 @@
         <v>6.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE7" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AF7" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AG7" t="n">
         <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
         <v>700</v>
       </c>
       <c r="AJ7" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
         <v>24</v>
@@ -2229,7 +2229,7 @@
         <v>700</v>
       </c>
       <c r="AN7" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO7" t="n">
         <v>700</v>
@@ -2238,34 +2238,34 @@
         <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX7" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>7.8</v>
       </c>
       <c r="AY7" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BA7" t="n">
         <v>9.199999999999999</v>
@@ -2277,22 +2277,22 @@
         <v>19</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF7" t="n">
         <v>14.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BJ7" t="n">
         <v>12.5</v>
@@ -2304,16 +2304,16 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ7" t="n">
         <v>6.4</v>
@@ -2322,35 +2322,35 @@
         <v>38</v>
       </c>
       <c r="BS7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BT7" t="n">
+      <c r="BU7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>65</v>
+      </c>
+      <c r="BW7" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BU7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>70</v>
-      </c>
-      <c r="BW7" t="n">
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
         <v>10</v>
       </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>2.16</v>
@@ -2390,13 +2390,13 @@
         <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.49</v>
@@ -2405,13 +2405,13 @@
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="O8" t="n">
         <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q8" t="n">
         <v>2.3</v>
@@ -2426,10 +2426,10 @@
         <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
         <v>1.86</v>
@@ -2495,16 +2495,16 @@
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="AS8" t="n">
         <v>7.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
         <v>15.5</v>
@@ -2516,7 +2516,7 @@
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
         <v>17.5</v>
@@ -2531,7 +2531,7 @@
         <v>6.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE8" t="n">
         <v>7.8</v>
@@ -2546,7 +2546,7 @@
         <v>3.05</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ8" t="n">
         <v>11.5</v>
@@ -2582,7 +2582,7 @@
         <v>8</v>
       </c>
       <c r="BU8" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BV8" t="n">
         <v>44</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -2638,55 +2638,55 @@
         <v>1.69</v>
       </c>
       <c r="G9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
         <v>1.42</v>
       </c>
       <c r="P9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
         <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V9" t="n">
         <v>1.16</v>
       </c>
       <c r="W9" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X9" t="n">
         <v>970</v>
@@ -2701,7 +2701,7 @@
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AC9" t="n">
         <v>15</v>
@@ -2716,7 +2716,7 @@
         <v>40</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AH9" t="n">
         <v>500</v>
@@ -2740,70 +2740,70 @@
         <v>85</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR9" t="n">
         <v>2.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="AU9" t="n">
         <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.96</v>
+        <v>8.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AX9" t="n">
         <v>7.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.46</v>
+        <v>8.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.75</v>
+        <v>8.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="BE9" t="n">
         <v>2.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK9" t="n">
         <v>5.7</v>
@@ -2812,53 +2812,53 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BN9" t="n">
         <v>4.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G10" t="n">
         <v>2.26</v>
@@ -2901,7 +2901,7 @@
         <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
         <v>3.45</v>
@@ -2934,7 +2934,7 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V10" t="n">
         <v>1.31</v>
@@ -2952,25 +2952,25 @@
         <v>28</v>
       </c>
       <c r="AA10" t="n">
-        <v>290</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC10" t="n">
         <v>7.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE10" t="n">
         <v>85</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
         <v>22</v>
@@ -2988,67 +2988,67 @@
         <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
         <v>26</v>
       </c>
       <c r="AO10" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
         <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AV10" t="n">
         <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC10" t="n">
         <v>22</v>
       </c>
       <c r="BD10" t="n">
-        <v>9.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="BE10" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BG10" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH10" t="n">
         <v>2.92</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AH11" t="n">
         <v>34</v>
@@ -3257,10 +3257,10 @@
         <v>18.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT11" t="n">
         <v>5.4</v>
@@ -3269,40 +3269,40 @@
         <v>5.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AY11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB11" t="n">
         <v>6.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH11" t="n">
         <v>3.2</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -3421,10 +3421,10 @@
         <v>1.14</v>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="P12" t="n">
         <v>1.42</v>
@@ -3436,13 +3436,13 @@
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="V12" t="n">
         <v>1.89</v>
@@ -3457,7 +3457,7 @@
         <v>6.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA12" t="n">
         <v>26</v>
@@ -3469,7 +3469,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
         <v>46</v>
@@ -3514,7 +3514,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
@@ -3523,37 +3523,37 @@
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW12" t="n">
         <v>20</v>
       </c>
       <c r="AX12" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AY12" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA12" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG12" t="n">
         <v>19</v>
@@ -3568,7 +3568,7 @@
         <v>14</v>
       </c>
       <c r="BK12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3604,7 +3604,7 @@
         <v>17.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>2.12</v>
       </c>
       <c r="G13" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="H13" t="n">
         <v>2.42</v>
@@ -3663,10 +3663,10 @@
         <v>2.98</v>
       </c>
       <c r="J13" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="K13" t="n">
-        <v>8.6</v>
+        <v>5.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.12</v>
@@ -3684,7 +3684,7 @@
         <v>4.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="R13" t="n">
         <v>2.58</v>
@@ -3696,13 +3696,13 @@
         <v>1.23</v>
       </c>
       <c r="U13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W13" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="X13" t="n">
         <v>500</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>14</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
         <v>8.6</v>
@@ -3944,7 +3944,7 @@
         <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="T14" t="n">
         <v>1.77</v>
@@ -3968,7 +3968,7 @@
         <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="AB14" t="n">
         <v>22</v>
@@ -4076,19 +4076,19 @@
         <v>12</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN14" t="n">
         <v>4.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP14" t="n">
         <v>6.4</v>
@@ -4097,7 +4097,7 @@
         <v>5.5</v>
       </c>
       <c r="BR14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BS14" t="n">
         <v>8</v>
@@ -4106,19 +4106,19 @@
         <v>19</v>
       </c>
       <c r="BU14" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1.88</v>
       </c>
       <c r="G15" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="H15" t="n">
         <v>5.2</v>
@@ -4171,13 +4171,13 @@
         <v>5.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
         <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M15" t="n">
         <v>1.11</v>
@@ -4186,13 +4186,13 @@
         <v>2.74</v>
       </c>
       <c r="O15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P15" t="n">
         <v>1.58</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R15" t="n">
         <v>1.2</v>
@@ -4210,7 +4210,7 @@
         <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X15" t="n">
         <v>9.800000000000001</v>
@@ -4273,7 +4273,7 @@
         <v>12</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="AS15" t="n">
         <v>9</v>
@@ -4315,7 +4315,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BG15" t="n">
         <v>9</v>
@@ -4330,7 +4330,7 @@
         <v>12.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-01 22:21:27</t>
+          <t>2026-07-02 00:31:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="H2" t="n">
         <v>1.32</v>
@@ -875,13 +875,13 @@
         <v>6.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O2" t="n">
         <v>1.18</v>
@@ -890,19 +890,19 @@
         <v>2.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R2" t="n">
         <v>1.66</v>
       </c>
       <c r="S2" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
         <v>3.9</v>
@@ -914,13 +914,13 @@
         <v>29</v>
       </c>
       <c r="Y2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AB2" t="n">
         <v>100</v>
@@ -929,28 +929,28 @@
         <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AF2" t="n">
         <v>110</v>
       </c>
       <c r="AG2" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AH2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="AK2" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AL2" t="n">
         <v>260</v>
@@ -962,25 +962,25 @@
         <v>150</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AP2" t="n">
         <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
         <v>36</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AV2" t="n">
         <v>9.4</v>
@@ -989,7 +989,7 @@
         <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="AY2" t="n">
         <v>32</v>
@@ -998,28 +998,28 @@
         <v>23</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BD2" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>18.5</v>
+        <v>40</v>
       </c>
       <c r="BF2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI2" t="n">
         <v>4.1</v>
@@ -1028,31 +1028,31 @@
         <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="BO2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>3.35</v>
+        <v>5.7</v>
       </c>
       <c r="BT2" t="n">
         <v>3.8</v>
@@ -1061,16 +1061,16 @@
         <v>3.65</v>
       </c>
       <c r="BV2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -1111,124 +1111,124 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
         <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
         <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R3" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T3" t="n">
         <v>1.59</v>
       </c>
       <c r="U3" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X3" t="n">
         <v>38</v>
       </c>
       <c r="Y3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z3" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AA3" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>23</v>
       </c>
-      <c r="AE3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>29</v>
-      </c>
       <c r="AK3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
         <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AO3" t="n">
         <v>48</v>
       </c>
       <c r="AP3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>19</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AR3" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AS3" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AT3" t="n">
         <v>11</v>
@@ -1237,40 +1237,40 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AX3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BB3" t="n">
         <v>17</v>
       </c>
       <c r="BC3" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BH3" t="n">
         <v>4.6</v>
@@ -1279,37 +1279,37 @@
         <v>4</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO3" t="n">
         <v>4.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR3" t="n">
         <v>21</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU3" t="n">
         <v>5.8</v>
@@ -1318,13 +1318,13 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="I4" t="n">
         <v>1.34</v>
@@ -1380,37 +1380,37 @@
         <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O4" t="n">
         <v>1.05</v>
       </c>
       <c r="P4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="R4" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V4" t="n">
         <v>3.9</v>
@@ -1428,7 +1428,7 @@
         <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB4" t="n">
         <v>100</v>
@@ -1446,7 +1446,7 @@
         <v>140</v>
       </c>
       <c r="AG4" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AH4" t="n">
         <v>26</v>
@@ -1461,7 +1461,7 @@
         <v>230</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AM4" t="n">
         <v>55</v>
@@ -1470,103 +1470,103 @@
         <v>40</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AT4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AV4" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BB4" t="n">
         <v>6.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.8</v>
+        <v>21</v>
       </c>
       <c r="BF4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BH4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI4" t="n">
         <v>6.4</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BO4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT4" t="n">
         <v>5.9</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV4" t="n">
         <v>8.199999999999999</v>
@@ -1578,7 +1578,7 @@
         <v>13.5</v>
       </c>
       <c r="BY4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ4" t="n">
         <v>5.4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -1619,43 +1619,43 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I5" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
         <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
         <v>4.1</v>
@@ -1664,37 +1664,37 @@
         <v>2.22</v>
       </c>
       <c r="U5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V5" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
         <v>6.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>44</v>
+        <v>17.5</v>
       </c>
       <c r="AB5" t="n">
         <v>55</v>
       </c>
       <c r="AC5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="n">
         <v>9.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AF5" t="n">
         <v>400</v>
@@ -1703,79 +1703,79 @@
         <v>85</v>
       </c>
       <c r="AH5" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AK5" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AL5" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AM5" t="n">
         <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="AO5" t="n">
-        <v>29</v>
+        <v>13.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AR5" t="n">
         <v>7.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="AT5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU5" t="n">
         <v>8</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD5" t="n">
         <v>10.5</v>
       </c>
-      <c r="AX5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BE5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="BG5" t="n">
         <v>10</v>
@@ -1787,10 +1787,10 @@
         <v>2.62</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1814,13 +1814,13 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5" t="n">
         <v>3.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BV5" t="n">
         <v>11</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -1873,133 +1873,133 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="G6" t="n">
-        <v>2.32</v>
+        <v>1.97</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N6" t="n">
         <v>2.94</v>
       </c>
-      <c r="K6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.52</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U6" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="X6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF6" t="n">
         <v>11</v>
       </c>
-      <c r="Y6" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH6" t="n">
         <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AJ6" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AK6" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AL6" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AO6" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AW6" t="n">
         <v>6.4</v>
@@ -2008,7 +2008,7 @@
         <v>4.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AZ6" t="n">
         <v>5.5</v>
@@ -2017,86 +2017,86 @@
         <v>6.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE6" t="n">
         <v>6.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BG6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS6" t="n">
         <v>6.4</v>
       </c>
-      <c r="BH6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>44</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BT6" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BU6" t="n">
         <v>4.1</v>
       </c>
       <c r="BV6" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BZ6" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -2127,55 +2127,55 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G7" t="n">
         <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.51</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="O7" t="n">
         <v>1.45</v>
       </c>
       <c r="P7" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
         <v>2.36</v>
       </c>
       <c r="R7" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
         <v>4.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
         <v>2.24</v>
@@ -2184,16 +2184,16 @@
         <v>11</v>
       </c>
       <c r="Y7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AC7" t="n">
         <v>8.4</v>
@@ -2202,155 +2202,155 @@
         <v>25</v>
       </c>
       <c r="AE7" t="n">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="AF7" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG7" t="n">
         <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>700</v>
+        <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL7" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
         <v>700</v>
       </c>
       <c r="AN7" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AO7" t="n">
         <v>700</v>
       </c>
       <c r="AP7" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AX7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BE7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
         <v>14.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
         <v>11</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>9</v>
       </c>
       <c r="BT7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BV7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BZ7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="CA7" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P8" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Q8" t="n">
         <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S8" t="n">
         <v>4.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="X8" t="n">
         <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="AF8" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
         <v>27</v>
       </c>
       <c r="AK8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO8" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>17.5</v>
+        <v>7.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY8" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF8" t="n">
         <v>17.5</v>
       </c>
-      <c r="BA8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BG8" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH8" t="n">
         <v>3.05</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ8" t="n">
         <v>11.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BR8" t="n">
         <v>38</v>
       </c>
       <c r="BS8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT8" t="n">
         <v>8</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BX8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -2635,40 +2635,40 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.69</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.67</v>
-      </c>
       <c r="Q9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
         <v>1.25</v>
@@ -2677,22 +2677,22 @@
         <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="V9" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="Z9" t="n">
         <v>500</v>
@@ -2701,19 +2701,19 @@
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AE9" t="n">
         <v>700</v>
       </c>
       <c r="AF9" t="n">
-        <v>40</v>
+        <v>17.5</v>
       </c>
       <c r="AG9" t="n">
         <v>9.6</v>
@@ -2740,88 +2740,88 @@
         <v>85</v>
       </c>
       <c r="AO9" t="n">
-        <v>210</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
         <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.56</v>
+        <v>7.4</v>
       </c>
       <c r="AX9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>7.8</v>
       </c>
-      <c r="AY9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BA9" t="n">
-        <v>3.75</v>
+        <v>7.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.55</v>
+        <v>9.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF9" t="n">
         <v>7</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH9" t="n">
         <v>3.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ9" t="n">
         <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ9" t="n">
         <v>6</v>
@@ -2830,35 +2830,35 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -2889,55 +2889,55 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G10" t="n">
         <v>2.26</v>
       </c>
       <c r="H10" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.52</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="R10" t="n">
         <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
         <v>1.79</v>
@@ -2949,10 +2949,10 @@
         <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA10" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB10" t="n">
         <v>7.8</v>
@@ -2961,10 +2961,10 @@
         <v>7.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF10" t="n">
         <v>13</v>
@@ -2973,19 +2973,19 @@
         <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI10" t="n">
         <v>240</v>
       </c>
       <c r="AJ10" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AK10" t="n">
         <v>29</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
@@ -2994,7 +2994,7 @@
         <v>26</v>
       </c>
       <c r="AO10" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
         <v>8.800000000000001</v>
@@ -3003,22 +3003,22 @@
         <v>10</v>
       </c>
       <c r="AR10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU10" t="n">
         <v>6.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -3027,52 +3027,52 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="BB10" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BC10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
         <v>44</v>
       </c>
       <c r="BE10" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BF10" t="n">
         <v>22</v>
       </c>
       <c r="BG10" t="n">
-        <v>11.5</v>
+        <v>50</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ10" t="n">
         <v>11</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN10" t="n">
         <v>4.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP10" t="n">
         <v>17.5</v>
@@ -3087,13 +3087,13 @@
         <v>11</v>
       </c>
       <c r="BT10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV10" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
         <v>11</v>
@@ -3105,14 +3105,14 @@
         <v>12</v>
       </c>
       <c r="BZ10" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
         <v>11</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -3149,31 +3149,31 @@
         <v>1.57</v>
       </c>
       <c r="H11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I11" t="n">
         <v>8.6</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
         <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
         <v>2.22</v>
@@ -3185,10 +3185,10 @@
         <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="U11" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
         <v>1.13</v>
@@ -3203,31 +3203,31 @@
         <v>23</v>
       </c>
       <c r="Z11" t="n">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="AA11" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AB11" t="n">
         <v>6.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE11" t="n">
         <v>220</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG11" t="n">
         <v>9.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI11" t="n">
         <v>200</v>
@@ -3236,85 +3236,85 @@
         <v>14.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN11" t="n">
         <v>12</v>
       </c>
       <c r="AO11" t="n">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7.6</v>
+        <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ11" t="n">
         <v>13.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3326,16 +3326,16 @@
         <v>3.85</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BP11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS11" t="n">
         <v>8.199999999999999</v>
@@ -3344,7 +3344,7 @@
         <v>12.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3362,11 +3362,11 @@
         <v>25</v>
       </c>
       <c r="CA11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -3397,94 +3397,94 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="G12" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H12" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="I12" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L12" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N12" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="O12" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="P12" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S12" t="n">
         <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U12" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.2</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>11.5</v>
+        <v>500</v>
       </c>
       <c r="AA12" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AD12" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AF12" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AG12" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AH12" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AI12" t="n">
-        <v>200</v>
+        <v>460</v>
       </c>
       <c r="AJ12" t="n">
         <v>700</v>
@@ -3499,128 +3499,128 @@
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>32</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5</v>
+        <v>1.89</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>20</v>
+        <v>1.95</v>
       </c>
       <c r="AT12" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>1.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="AY12" t="n">
-        <v>19.5</v>
+        <v>1.97</v>
       </c>
       <c r="AZ12" t="n">
-        <v>22</v>
+        <v>1.89</v>
       </c>
       <c r="BA12" t="n">
-        <v>44</v>
+        <v>1.99</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.4</v>
+        <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>9.4</v>
+        <v>2.02</v>
       </c>
       <c r="BD12" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.6</v>
+        <v>2.02</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.6</v>
+        <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>19</v>
+        <v>6.2</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="BJ12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BK12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN12" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BO12" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.800000000000001</v>
+        <v>2.02</v>
       </c>
       <c r="BT12" t="n">
         <v>4.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="BV12" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G13" t="n">
         <v>2.46</v>
       </c>
       <c r="H13" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="I13" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>4.4</v>
@@ -3669,28 +3669,28 @@
         <v>5.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="O13" t="n">
         <v>1.05</v>
       </c>
       <c r="P13" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="Q13" t="n">
         <v>1.18</v>
       </c>
       <c r="R13" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="S13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T13" t="n">
         <v>1.23</v>
@@ -3699,7 +3699,7 @@
         <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.68</v>
@@ -3720,7 +3720,7 @@
         <v>500</v>
       </c>
       <c r="AC13" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD13" t="n">
         <v>500</v>
@@ -3732,10 +3732,10 @@
         <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AH13" t="n">
-        <v>970</v>
+        <v>100</v>
       </c>
       <c r="AI13" t="n">
         <v>500</v>
@@ -3753,55 +3753,55 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>55</v>
+        <v>6.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>55</v>
+        <v>7.8</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.04</v>
+        <v>5.9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.32</v>
+        <v>5.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.16</v>
+        <v>5.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.32</v>
+        <v>5.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="AV13" t="n">
         <v>4.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.26</v>
+        <v>5.1</v>
       </c>
       <c r="AX13" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>2.16</v>
+        <v>4.7</v>
       </c>
       <c r="AZ13" t="n">
         <v>4.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.12</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.22</v>
+        <v>5.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.12</v>
+        <v>5</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.92</v>
+        <v>4.9</v>
       </c>
       <c r="BE13" t="n">
         <v>5.2</v>
@@ -3813,13 +3813,13 @@
         <v>3.45</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI13" t="n">
         <v>3.85</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK13" t="n">
         <v>3.8</v>
@@ -3828,53 +3828,53 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.21</v>
+        <v>5.8</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO13" t="n">
         <v>3.7</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.77</v>
+        <v>4.8</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU13" t="n">
         <v>3.85</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.35</v>
+        <v>5</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.61</v>
+        <v>4.9</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -3905,25 +3905,25 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="G14" t="n">
         <v>1.2</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.22</v>
-      </c>
       <c r="H14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>10.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
@@ -3935,22 +3935,22 @@
         <v>1.08</v>
       </c>
       <c r="P14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q14" t="n">
         <v>1.27</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S14" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="T14" t="n">
         <v>1.77</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V14" t="n">
         <v>1.05</v>
@@ -3968,16 +3968,16 @@
         <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>590</v>
+        <v>620</v>
       </c>
       <c r="AB14" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AD14" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
@@ -4022,13 +4022,13 @@
         <v>46</v>
       </c>
       <c r="AS14" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="AT14" t="n">
         <v>17</v>
       </c>
       <c r="AU14" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV14" t="n">
         <v>27</v>
@@ -4061,7 +4061,7 @@
         <v>40</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BG14" t="n">
         <v>44</v>
@@ -4082,7 +4082,7 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN14" t="n">
         <v>4.5</v>
@@ -4100,10 +4100,10 @@
         <v>16.5</v>
       </c>
       <c r="BS14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BU14" t="n">
         <v>8.6</v>
@@ -4112,13 +4112,13 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>
@@ -4162,13 +4162,13 @@
         <v>1.88</v>
       </c>
       <c r="G15" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="H15" t="n">
         <v>5.2</v>
       </c>
       <c r="I15" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J15" t="n">
         <v>3.35</v>
@@ -4177,22 +4177,22 @@
         <v>3.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="M15" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P15" t="n">
         <v>1.58</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
         <v>1.2</v>
@@ -4204,13 +4204,13 @@
         <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W15" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X15" t="n">
         <v>9.800000000000001</v>
@@ -4297,7 +4297,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
         <v>8.800000000000001</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 00:31:26</t>
+          <t>2026-07-02 02:41:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="G2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="I2" t="n">
         <v>1.34</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K2" t="n">
         <v>6.6</v>
@@ -881,28 +881,28 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="S2" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
         <v>3.9</v>
@@ -911,22 +911,22 @@
         <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>12</v>
       </c>
       <c r="AB2" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AC2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD2" t="n">
         <v>11</v>
@@ -938,40 +938,40 @@
         <v>110</v>
       </c>
       <c r="AG2" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AH2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
         <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="AK2" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AL2" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN2" t="n">
         <v>150</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS2" t="n">
         <v>10</v>
@@ -983,13 +983,13 @@
         <v>12.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW2" t="n">
         <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>13.5</v>
+        <v>60</v>
       </c>
       <c r="AY2" t="n">
         <v>32</v>
@@ -998,43 +998,43 @@
         <v>23</v>
       </c>
       <c r="BA2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="BD2" t="n">
-        <v>13.5</v>
+        <v>55</v>
       </c>
       <c r="BE2" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BF2" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI2" t="n">
         <v>4.1</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="BN2" t="n">
         <v>13</v>
@@ -1046,13 +1046,13 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.3</v>
+        <v>13</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="BT2" t="n">
         <v>3.8</v>
@@ -1067,10 +1067,10 @@
         <v>6</v>
       </c>
       <c r="BX2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BY2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="G3" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
         <v>4.4</v>
@@ -1150,19 +1150,19 @@
         <v>1.66</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U3" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="X3" t="n">
         <v>38</v>
@@ -1171,13 +1171,13 @@
         <v>27</v>
       </c>
       <c r="Z3" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA3" t="n">
         <v>170</v>
       </c>
       <c r="AB3" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AC3" t="n">
         <v>12.5</v>
@@ -1189,19 +1189,19 @@
         <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AI3" t="n">
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK3" t="n">
         <v>23</v>
@@ -1210,10 +1210,10 @@
         <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AN3" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO3" t="n">
         <v>48</v>
@@ -1222,10 +1222,10 @@
         <v>16.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AS3" t="n">
         <v>55</v>
@@ -1237,16 +1237,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AX3" t="n">
         <v>12</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
@@ -1258,19 +1258,19 @@
         <v>17</v>
       </c>
       <c r="BC3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BE3" t="n">
         <v>50</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BG3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH3" t="n">
         <v>4.6</v>
@@ -1282,13 +1282,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
         <v>5</v>
@@ -1300,13 +1300,13 @@
         <v>11.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR3" t="n">
         <v>21</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT3" t="n">
         <v>8.199999999999999</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="G4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="I4" t="n">
         <v>1.34</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K4" t="n">
         <v>7.8</v>
@@ -1395,25 +1395,25 @@
         <v>1.05</v>
       </c>
       <c r="P4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="R4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="U4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="W4" t="n">
         <v>1.12</v>
@@ -1452,10 +1452,10 @@
         <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AJ4" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AK4" t="n">
         <v>230</v>
@@ -1470,13 +1470,13 @@
         <v>40</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR4" t="n">
         <v>18</v>
@@ -1485,10 +1485,10 @@
         <v>16</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
         <v>12.5</v>
@@ -1497,10 +1497,10 @@
         <v>12</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>12</v>
+        <v>5.9</v>
       </c>
       <c r="AZ4" t="n">
         <v>18</v>
@@ -1509,28 +1509,28 @@
         <v>17</v>
       </c>
       <c r="BB4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC4" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC4" t="n">
-        <v>27</v>
-      </c>
       <c r="BD4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG4" t="n">
         <v>2.36</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.6</v>
@@ -1554,22 +1554,22 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS4" t="n">
         <v>8.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BV4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BW4" t="n">
         <v>6</v>
@@ -1581,14 +1581,14 @@
         <v>6.2</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CA4" t="n">
         <v>4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -1631,10 +1631,10 @@
         <v>1.61</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.47</v>
@@ -1649,7 +1649,7 @@
         <v>1.39</v>
       </c>
       <c r="P5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
         <v>2.2</v>
@@ -1664,13 +1664,13 @@
         <v>2.22</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V5" t="n">
         <v>2.62</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
@@ -1682,13 +1682,13 @@
         <v>9.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AB5" t="n">
         <v>55</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
         <v>9.6</v>
@@ -1724,10 +1724,10 @@
         <v>660</v>
       </c>
       <c r="AO5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.9</v>
@@ -1736,10 +1736,10 @@
         <v>7.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU5" t="n">
         <v>8</v>
@@ -1751,10 +1751,10 @@
         <v>13.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
         <v>21</v>
@@ -1763,19 +1763,19 @@
         <v>30</v>
       </c>
       <c r="BB5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BE5" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
         <v>10</v>
@@ -1790,7 +1790,7 @@
         <v>13</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1814,13 +1814,13 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT5" t="n">
         <v>3.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BV5" t="n">
         <v>11</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -1873,55 +1873,55 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="G6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I6" t="n">
         <v>5.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.51</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="V6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
         <v>2.02</v>
@@ -1930,173 +1930,173 @@
         <v>12</v>
       </c>
       <c r="Y6" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AG6" t="n">
         <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
         <v>260</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>280</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AR6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT6" t="n">
         <v>6</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AU6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW6" t="n">
         <v>6.6</v>
       </c>
-      <c r="AT6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AX6" t="n">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.3</v>
+        <v>19.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.4</v>
+        <v>19.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BH6" t="n">
         <v>3.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>7.4</v>
+        <v>2.26</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="BP6" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BR6" t="n">
         <v>38</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.4</v>
+        <v>2.16</v>
       </c>
       <c r="BT6" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BV6" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.8</v>
+        <v>2.18</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY6" t="n">
-        <v>7</v>
+        <v>2.2</v>
       </c>
       <c r="BZ6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.4</v>
+        <v>2.16</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H7" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
         <v>3.9</v>
@@ -2148,37 +2148,37 @@
         <v>1.51</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O7" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S7" t="n">
         <v>4.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X7" t="n">
         <v>11</v>
@@ -2187,13 +2187,13 @@
         <v>16.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC7" t="n">
         <v>8.4</v>
@@ -2202,22 +2202,22 @@
         <v>25</v>
       </c>
       <c r="AE7" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AF7" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AG7" t="n">
         <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
         <v>240</v>
       </c>
       <c r="AJ7" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
         <v>25</v>
@@ -2229,46 +2229,46 @@
         <v>700</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AO7" t="n">
         <v>700</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AX7" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="BB7" t="n">
         <v>16.5</v>
@@ -2277,34 +2277,34 @@
         <v>19.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG7" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH7" t="n">
         <v>2.96</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="BJ7" t="n">
         <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BN7" t="n">
         <v>4.1</v>
@@ -2313,44 +2313,44 @@
         <v>3.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="CA7" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="G8" t="n">
         <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.5</v>
@@ -2405,142 +2405,142 @@
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
         <v>4.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="U8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V8" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="X8" t="n">
         <v>11</v>
       </c>
       <c r="Y8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF8" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AK8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO8" t="n">
-        <v>600</v>
+        <v>280</v>
       </c>
       <c r="AP8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
         <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="BB8" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF8" t="n">
         <v>20</v>
       </c>
-      <c r="BC8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BG8" t="n">
-        <v>8.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BH8" t="n">
         <v>3.05</v>
@@ -2549,7 +2549,7 @@
         <v>2.66</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK8" t="n">
         <v>7.8</v>
@@ -2561,13 +2561,13 @@
         <v>10.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BQ8" t="n">
         <v>10</v>
@@ -2579,22 +2579,22 @@
         <v>8.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BV8" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BW8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX8" t="n">
         <v>65</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>36</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -2635,64 +2635,64 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="G9" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="O9" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="P9" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W9" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="X9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="Z9" t="n">
         <v>500</v>
@@ -2701,34 +2701,34 @@
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AE9" t="n">
         <v>700</v>
       </c>
       <c r="AF9" t="n">
-        <v>17.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG9" t="n">
         <v>9.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AI9" t="n">
         <v>700</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>23</v>
       </c>
       <c r="AK9" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
         <v>500</v>
@@ -2737,91 +2737,91 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="AO9" t="n">
-        <v>600</v>
+        <v>320</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>9</v>
+        <v>19.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AU9" t="n">
         <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>7.6</v>
+        <v>17.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="BE9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>60</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BN9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BP9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ9" t="n">
         <v>6</v>
@@ -2830,35 +2830,35 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA9" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="G10" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="H10" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
         <v>1.52</v>
@@ -2913,121 +2913,121 @@
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="O10" t="n">
         <v>1.47</v>
       </c>
       <c r="P10" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
         <v>4.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="X10" t="n">
         <v>10.5</v>
       </c>
       <c r="Y10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>13</v>
-      </c>
       <c r="AG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>240</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN10" t="n">
+      <c r="AR10" t="n">
         <v>26</v>
       </c>
-      <c r="AO10" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="AS10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX10" t="n">
         <v>10</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>11</v>
       </c>
       <c r="AY10" t="n">
         <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA10" t="n">
         <v>50</v>
@@ -3036,70 +3036,70 @@
         <v>22</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
         <v>44</v>
       </c>
       <c r="BE10" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BG10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH10" t="n">
         <v>2.9</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="BP10" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BR10" t="n">
         <v>38</v>
       </c>
       <c r="BS10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW10" t="n">
         <v>11</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY10" t="n">
         <v>12</v>
@@ -3108,11 +3108,11 @@
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -3146,22 +3146,22 @@
         <v>1.52</v>
       </c>
       <c r="G11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H11" t="n">
         <v>7.6</v>
       </c>
       <c r="I11" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
         <v>4.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
@@ -3170,16 +3170,16 @@
         <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
         <v>2.22</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
         <v>4.3</v>
@@ -3188,7 +3188,7 @@
         <v>2.26</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
         <v>1.13</v>
@@ -3197,7 +3197,7 @@
         <v>2.74</v>
       </c>
       <c r="X11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="n">
         <v>23</v>
@@ -3206,7 +3206,7 @@
         <v>170</v>
       </c>
       <c r="AA11" t="n">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="AB11" t="n">
         <v>6.6</v>
@@ -3230,52 +3230,52 @@
         <v>32</v>
       </c>
       <c r="AI11" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AJ11" t="n">
         <v>14.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AN11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
         <v>11.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="AW11" t="n">
         <v>11.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AY11" t="n">
         <v>8</v>
@@ -3287,28 +3287,28 @@
         <v>11.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>27</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE11" t="n">
         <v>11.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BG11" t="n">
         <v>11.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BJ11" t="n">
         <v>13.5</v>
@@ -3320,37 +3320,37 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.199999999999999</v>
+        <v>2.84</v>
       </c>
       <c r="BN11" t="n">
         <v>3.85</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BP11" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT11" t="n">
         <v>12.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -3397,40 +3397,40 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="G12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I12" t="n">
         <v>1.93</v>
       </c>
-      <c r="I12" t="n">
-        <v>2.02</v>
-      </c>
       <c r="J12" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
         <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N12" t="n">
         <v>2.42</v>
       </c>
       <c r="O12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P12" t="n">
         <v>1.45</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="R12" t="n">
         <v>1.17</v>
@@ -3439,52 +3439,52 @@
         <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V12" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB12" t="n">
         <v>14</v>
       </c>
-      <c r="Y12" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>970</v>
-      </c>
       <c r="AC12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>180</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH12" t="n">
         <v>42</v>
       </c>
-      <c r="AD12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>500</v>
-      </c>
       <c r="AI12" t="n">
-        <v>460</v>
+        <v>200</v>
       </c>
       <c r="AJ12" t="n">
         <v>700</v>
@@ -3499,128 +3499,128 @@
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AO12" t="n">
-        <v>600</v>
+        <v>28</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.89</v>
+        <v>4.8</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.95</v>
+        <v>18</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.9</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.97</v>
+        <v>21</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.89</v>
+        <v>10</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.99</v>
+        <v>28</v>
       </c>
       <c r="BB12" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.02</v>
+        <v>7.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.02</v>
+        <v>9</v>
       </c>
       <c r="BF12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="BI12" t="n">
         <v>2.14</v>
       </c>
       <c r="BJ12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BO12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT12" t="n">
         <v>4.4</v>
       </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BU12" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="BV12" t="n">
         <v>16.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BX12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -3651,55 +3651,55 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
         <v>2.46</v>
       </c>
       <c r="H13" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K13" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="R13" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="S13" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T13" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W13" t="n">
         <v>1.68</v>
@@ -3714,7 +3714,7 @@
         <v>500</v>
       </c>
       <c r="AA13" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
         <v>500</v>
@@ -3723,7 +3723,7 @@
         <v>42</v>
       </c>
       <c r="AD13" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE13" t="n">
         <v>500</v>
@@ -3732,16 +3732,16 @@
         <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AI13" t="n">
         <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>500</v>
@@ -3753,128 +3753,128 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AP13" t="n">
         <v>6.4</v>
       </c>
-      <c r="AO13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AP13" t="n">
+      <c r="AQ13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY13" t="n">
         <v>5.9</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>5.6</v>
       </c>
-      <c r="AR13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BD13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI13" t="n">
         <v>4.9</v>
       </c>
-      <c r="BE13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BJ13" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BK13" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BN13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BO13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BU13" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BV13" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BX13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BZ13" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -3911,10 +3911,10 @@
         <v>1.2</v>
       </c>
       <c r="H14" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
         <v>9.199999999999999</v>
@@ -3941,16 +3941,16 @@
         <v>1.27</v>
       </c>
       <c r="R14" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="T14" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
         <v>1.05</v>
@@ -3968,28 +3968,28 @@
         <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>620</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AD14" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -4001,28 +4001,28 @@
         <v>13.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
         <v>490</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AQ14" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AR14" t="n">
         <v>46</v>
       </c>
       <c r="AS14" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AT14" t="n">
         <v>17</v>
@@ -4031,7 +4031,7 @@
         <v>20</v>
       </c>
       <c r="AV14" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AW14" t="n">
         <v>46</v>
@@ -4055,13 +4055,13 @@
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="BG14" t="n">
         <v>44</v>
@@ -4076,16 +4076,16 @@
         <v>12</v>
       </c>
       <c r="BK14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO14" t="n">
         <v>3.55</v>
@@ -4100,25 +4100,25 @@
         <v>16.5</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT14" t="n">
         <v>18.5</v>
       </c>
       <c r="BU14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>
@@ -4162,16 +4162,16 @@
         <v>1.88</v>
       </c>
       <c r="G15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H15" t="n">
         <v>5.2</v>
       </c>
       <c r="I15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
         <v>3.5</v>
@@ -4189,25 +4189,25 @@
         <v>1.52</v>
       </c>
       <c r="P15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R15" t="n">
         <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U15" t="n">
         <v>1.74</v>
       </c>
       <c r="V15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
         <v>2.08</v>
@@ -4216,7 +4216,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z15" t="n">
         <v>44</v>
@@ -4276,7 +4276,7 @@
         <v>34</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT15" t="n">
         <v>5.6</v>
@@ -4288,7 +4288,7 @@
         <v>19</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX15" t="n">
         <v>8.6</v>
@@ -4300,7 +4300,7 @@
         <v>21</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB15" t="n">
         <v>18.5</v>
@@ -4309,19 +4309,19 @@
         <v>21</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF15" t="n">
         <v>18</v>
       </c>
       <c r="BG15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BI15" t="n">
         <v>2.36</v>
@@ -4354,7 +4354,7 @@
         <v>40</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT15" t="n">
         <v>9</v>
@@ -4366,7 +4366,7 @@
         <v>60</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX15" t="n">
         <v>80</v>
@@ -4378,11 +4378,11 @@
         <v>40</v>
       </c>
       <c r="CA15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 02:41:28</t>
+          <t>2026-07-02 04:51:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -857,82 +857,82 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="G2" t="n">
         <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="I2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="S2" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AA2" t="n">
         <v>12</v>
       </c>
       <c r="AB2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AC2" t="n">
         <v>15</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF2" t="n">
         <v>110</v>
@@ -941,40 +941,40 @@
         <v>38</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AJ2" t="n">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="AK2" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AL2" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AM2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN2" t="n">
         <v>120</v>
       </c>
-      <c r="AN2" t="n">
-        <v>150</v>
-      </c>
       <c r="AO2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
         <v>36</v>
@@ -983,94 +983,94 @@
         <v>12.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AY2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AZ2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BD2" t="n">
         <v>55</v>
       </c>
       <c r="BE2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF2" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN2" t="n">
         <v>13</v>
       </c>
       <c r="BO2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>3.45</v>
+        <v>12.5</v>
       </c>
       <c r="BT2" t="n">
         <v>3.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BV2" t="n">
         <v>7.6</v>
       </c>
       <c r="BW2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>1.83</v>
       </c>
       <c r="G3" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="H3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
         <v>4.2</v>
@@ -1126,7 +1126,7 @@
         <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.28</v>
@@ -1141,55 +1141,55 @@
         <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="Q3" t="n">
         <v>1.55</v>
       </c>
       <c r="R3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S3" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="T3" t="n">
         <v>1.58</v>
       </c>
       <c r="U3" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V3" t="n">
         <v>1.31</v>
       </c>
       <c r="W3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X3" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Y3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Z3" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AA3" t="n">
         <v>170</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
         <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AG3" t="n">
         <v>10.5</v>
@@ -1198,10 +1198,10 @@
         <v>17</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK3" t="n">
         <v>23</v>
@@ -1210,22 +1210,22 @@
         <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO3" t="n">
         <v>48</v>
       </c>
       <c r="AP3" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AQ3" t="n">
         <v>18</v>
       </c>
       <c r="AR3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS3" t="n">
         <v>55</v>
@@ -1249,13 +1249,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
         <v>32</v>
       </c>
       <c r="BB3" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BC3" t="n">
         <v>14</v>
@@ -1267,10 +1267,10 @@
         <v>50</v>
       </c>
       <c r="BF3" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BH3" t="n">
         <v>4.6</v>
@@ -1282,13 +1282,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN3" t="n">
         <v>5</v>
@@ -1300,10 +1300,10 @@
         <v>11.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
         <v>9</v>
@@ -1318,13 +1318,13 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K4" t="n">
         <v>8.4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="J4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>7.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.12</v>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
         <v>1.05</v>
@@ -1401,37 +1401,37 @@
         <v>1.16</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T4" t="n">
         <v>1.38</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V4" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="Y4" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="Z4" t="n">
         <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB4" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="AC4" t="n">
         <v>30</v>
@@ -1446,7 +1446,7 @@
         <v>140</v>
       </c>
       <c r="AG4" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AH4" t="n">
         <v>26</v>
@@ -1455,7 +1455,7 @@
         <v>21</v>
       </c>
       <c r="AJ4" t="n">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="AK4" t="n">
         <v>230</v>
@@ -1464,19 +1464,19 @@
         <v>150</v>
       </c>
       <c r="AM4" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AN4" t="n">
         <v>40</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AR4" t="n">
         <v>18</v>
@@ -1485,22 +1485,22 @@
         <v>16</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="AZ4" t="n">
         <v>18</v>
@@ -1509,58 +1509,58 @@
         <v>17</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BF4" t="n">
         <v>10.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="BH4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
         <v>14</v>
       </c>
       <c r="BO4" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BR4" t="n">
         <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>5.8</v>
@@ -1572,23 +1572,23 @@
         <v>8</v>
       </c>
       <c r="BW4" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BX4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BY4" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="CA4" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -1619,25 +1619,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="G5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="I5" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1646,55 +1646,55 @@
         <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
         <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="U5" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="V5" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
         <v>6.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AB5" t="n">
         <v>55</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>9.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF5" t="n">
         <v>400</v>
@@ -1703,43 +1703,43 @@
         <v>85</v>
       </c>
       <c r="AH5" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AI5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>290</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>370</v>
-      </c>
       <c r="AK5" t="n">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="AL5" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="AM5" t="n">
         <v>700</v>
       </c>
       <c r="AN5" t="n">
-        <v>660</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU5" t="n">
         <v>8</v>
@@ -1748,43 +1748,43 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB5" t="n">
-        <v>11.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BD5" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="BE5" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BF5" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ5" t="n">
         <v>13</v>
@@ -1799,10 +1799,10 @@
         <v>10.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1817,16 +1817,16 @@
         <v>10</v>
       </c>
       <c r="BT5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1838,11 +1838,11 @@
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -1879,46 +1879,46 @@
         <v>1.98</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P6" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U6" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="V6" t="n">
         <v>1.25</v>
@@ -1927,31 +1927,31 @@
         <v>2.02</v>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
         <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
         <v>85</v>
       </c>
       <c r="AF6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
         <v>11.5</v>
@@ -1960,143 +1960,143 @@
         <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>260</v>
+        <v>95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AO6" t="n">
         <v>280</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
         <v>6</v>
       </c>
       <c r="AU6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW6" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW6" t="n">
+      <c r="AX6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA6" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BB6" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BC6" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BG6" t="n">
         <v>10</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BJ6" t="n">
         <v>12</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.26</v>
+        <v>7.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BP6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.16</v>
+        <v>6.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.18</v>
+        <v>6.8</v>
       </c>
       <c r="BX6" t="n">
         <v>65</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.2</v>
+        <v>7</v>
       </c>
       <c r="BZ6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.16</v>
+        <v>6.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -2127,37 +2127,37 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="G7" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="I7" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
         <v>2.34</v>
@@ -2169,55 +2169,55 @@
         <v>4.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="W7" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="X7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF7" t="n">
         <v>11</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>10</v>
       </c>
       <c r="AG7" t="n">
         <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>240</v>
+        <v>95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
         <v>25</v>
@@ -2226,79 +2226,79 @@
         <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>700</v>
+        <v>220</v>
       </c>
       <c r="AN7" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AP7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AW7" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AX7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA7" t="n">
         <v>46</v>
       </c>
       <c r="BB7" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="BE7" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BF7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BI7" t="n">
         <v>2.6</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2307,50 +2307,50 @@
         <v>12.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BP7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR7" t="n">
         <v>38</v>
       </c>
       <c r="BS7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G8" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
         <v>3.5</v>
@@ -2405,112 +2405,112 @@
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="X8" t="n">
         <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
         <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC8" t="n">
         <v>7.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF8" t="n">
         <v>13.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
         <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="AP8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
@@ -2540,7 +2540,7 @@
         <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH8" t="n">
         <v>3.05</v>
@@ -2558,13 +2558,13 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN8" t="n">
         <v>5</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP8" t="n">
         <v>18</v>
@@ -2576,16 +2576,16 @@
         <v>38</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU8" t="n">
         <v>6</v>
       </c>
       <c r="BV8" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BW8" t="n">
         <v>8.800000000000001</v>
@@ -2594,17 +2594,17 @@
         <v>65</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ8" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="CA8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -2635,97 +2635,97 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="P9" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="U9" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="V9" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W9" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="X9" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
         <v>700</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AG9" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI9" t="n">
         <v>700</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK9" t="n">
         <v>34</v>
@@ -2740,125 +2740,125 @@
         <v>24</v>
       </c>
       <c r="AO9" t="n">
-        <v>320</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS9" t="n">
         <v>9</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AT9" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW9" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY9" t="n">
         <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="BB9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF9" t="n">
         <v>13.5</v>
       </c>
-      <c r="BC9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>12</v>
-      </c>
       <c r="BG9" t="n">
-        <v>60</v>
+        <v>10.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BJ9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BP9" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -2889,175 +2889,175 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.04</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="X10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG10" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>11</v>
-      </c>
       <c r="AH10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK10" t="n">
         <v>24</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>27</v>
       </c>
       <c r="AL10" t="n">
         <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN10" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AP10" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AS10" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT10" t="n">
         <v>6</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX10" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
         <v>21</v>
       </c>
       <c r="BA10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB10" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE10" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BF10" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK10" t="n">
         <v>8.4</v>
@@ -3066,53 +3066,53 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BP10" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>70</v>
+      </c>
+      <c r="BW10" t="n">
         <v>10.5</v>
       </c>
-      <c r="BT10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>48</v>
-      </c>
-      <c r="BW10" t="n">
+      <c r="BX10" t="n">
+        <v>95</v>
+      </c>
+      <c r="BY10" t="n">
         <v>11</v>
       </c>
-      <c r="BX10" t="n">
-        <v>75</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>12</v>
-      </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA10" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G11" t="n">
         <v>1.58</v>
       </c>
       <c r="H11" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
@@ -3170,7 +3170,7 @@
         <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
         <v>1.73</v>
@@ -3179,37 +3179,37 @@
         <v>2.22</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
         <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X11" t="n">
         <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z11" t="n">
         <v>170</v>
       </c>
       <c r="AA11" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC11" t="n">
         <v>9.800000000000001</v>
@@ -3218,7 +3218,7 @@
         <v>36</v>
       </c>
       <c r="AE11" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AF11" t="n">
         <v>8</v>
@@ -3230,7 +3230,7 @@
         <v>32</v>
       </c>
       <c r="AI11" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AJ11" t="n">
         <v>14.5</v>
@@ -3242,13 +3242,13 @@
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO11" t="n">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
@@ -3257,22 +3257,22 @@
         <v>18.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AS11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT11" t="n">
         <v>4.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="AW11" t="n">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="AX11" t="n">
         <v>6.8</v>
@@ -3281,28 +3281,28 @@
         <v>8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BB11" t="n">
         <v>11.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BE11" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="BF11" t="n">
         <v>10</v>
       </c>
       <c r="BG11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH11" t="n">
         <v>3.2</v>
@@ -3314,28 +3314,28 @@
         <v>13.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BN11" t="n">
         <v>3.85</v>
       </c>
       <c r="BO11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP11" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS11" t="n">
         <v>8.6</v>
@@ -3344,7 +3344,7 @@
         <v>12.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
@@ -3362,11 +3362,11 @@
         <v>25</v>
       </c>
       <c r="CA11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -3397,40 +3397,40 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="G12" t="n">
         <v>6.4</v>
       </c>
       <c r="H12" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="I12" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N12" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="O12" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="P12" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
         <v>1.17</v>
@@ -3439,58 +3439,58 @@
         <v>6.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="U12" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="V12" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="W12" t="n">
         <v>1.19</v>
       </c>
       <c r="X12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y12" t="n">
         <v>6.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AB12" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH12" t="n">
         <v>34</v>
       </c>
-      <c r="AF12" t="n">
-        <v>180</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>42</v>
-      </c>
       <c r="AI12" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AJ12" t="n">
         <v>700</v>
       </c>
       <c r="AK12" t="n">
-        <v>700</v>
+        <v>190</v>
       </c>
       <c r="AL12" t="n">
         <v>700</v>
@@ -3499,128 +3499,128 @@
         <v>500</v>
       </c>
       <c r="AN12" t="n">
-        <v>370</v>
+        <v>890</v>
       </c>
       <c r="AO12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AR12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AS12" t="n">
         <v>18</v>
       </c>
       <c r="AT12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV12" t="n">
         <v>10.5</v>
       </c>
-      <c r="AU12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AW12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AX12" t="n">
         <v>34</v>
       </c>
       <c r="AY12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="BA12" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.2</v>
+        <v>75</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.2</v>
+        <v>75</v>
       </c>
       <c r="BE12" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="BF12" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BH12" t="n">
         <v>2.7</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BJ12" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BV12" t="n">
         <v>16.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -3651,58 +3651,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="G13" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H13" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="I13" t="n">
         <v>2.86</v>
       </c>
       <c r="J13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K13" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="O13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P13" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="R13" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="S13" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="T13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="U13" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="V13" t="n">
         <v>1.54</v>
       </c>
       <c r="W13" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X13" t="n">
         <v>500</v>
@@ -3714,13 +3714,13 @@
         <v>500</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB13" t="n">
         <v>500</v>
       </c>
       <c r="AC13" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AD13" t="n">
         <v>970</v>
@@ -3741,7 +3741,7 @@
         <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK13" t="n">
         <v>500</v>
@@ -3753,128 +3753,128 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG13" t="n">
         <v>6.2</v>
       </c>
-      <c r="AO13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>4</v>
-      </c>
       <c r="BH13" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BJ13" t="n">
         <v>8</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN13" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BT13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BZ13" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -3905,25 +3905,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="H14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I14" t="n">
         <v>15.5</v>
       </c>
-      <c r="I14" t="n">
-        <v>18</v>
-      </c>
       <c r="J14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="K14" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
@@ -3932,31 +3932,31 @@
         <v>11</v>
       </c>
       <c r="O14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P14" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="S14" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="X14" t="n">
         <v>490</v>
@@ -3968,28 +3968,28 @@
         <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB14" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AD14" t="n">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG14" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -4001,52 +4001,52 @@
         <v>13.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM14" t="n">
         <v>490</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AQ14" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AR14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS14" t="n">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AT14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU14" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AW14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BB14" t="n">
         <v>10</v>
@@ -4055,34 +4055,34 @@
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="BG14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BI14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BJ14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN14" t="n">
         <v>4.6</v>
@@ -4091,7 +4091,7 @@
         <v>3.55</v>
       </c>
       <c r="BP14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BQ14" t="n">
         <v>5.5</v>
@@ -4100,25 +4100,25 @@
         <v>16.5</v>
       </c>
       <c r="BS14" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BT14" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BU14" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>
@@ -4162,22 +4162,22 @@
         <v>1.88</v>
       </c>
       <c r="G15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J15" t="n">
         <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M15" t="n">
         <v>1.12</v>
@@ -4186,7 +4186,7 @@
         <v>2.78</v>
       </c>
       <c r="O15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P15" t="n">
         <v>1.57</v>
@@ -4198,7 +4198,7 @@
         <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T15" t="n">
         <v>2.22</v>
@@ -4213,19 +4213,19 @@
         <v>2.08</v>
       </c>
       <c r="X15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y15" t="n">
         <v>14</v>
       </c>
       <c r="Z15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA15" t="n">
         <v>200</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC15" t="n">
         <v>8</v>
@@ -4264,7 +4264,7 @@
         <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AP15" t="n">
         <v>8</v>
@@ -4276,10 +4276,10 @@
         <v>34</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU15" t="n">
         <v>6.8</v>
@@ -4288,7 +4288,7 @@
         <v>19</v>
       </c>
       <c r="AW15" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX15" t="n">
         <v>8.6</v>
@@ -4300,7 +4300,7 @@
         <v>21</v>
       </c>
       <c r="BA15" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB15" t="n">
         <v>18.5</v>
@@ -4309,16 +4309,16 @@
         <v>21</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF15" t="n">
         <v>18</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.199999999999999</v>
+        <v>200</v>
       </c>
       <c r="BH15" t="n">
         <v>2.86</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 04:51:47</t>
+          <t>2026-07-02 07:01:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,43 +857,43 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H2" t="n">
         <v>1.32</v>
       </c>
       <c r="I2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="J2" t="n">
         <v>6</v>
       </c>
       <c r="K2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N2" t="n">
         <v>6.8</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N2" t="n">
-        <v>6.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S2" t="n">
         <v>2.2</v>
@@ -902,16 +902,16 @@
         <v>1.8</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y2" t="n">
         <v>12.5</v>
@@ -929,61 +929,61 @@
         <v>15</v>
       </c>
       <c r="AD2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF2" t="n">
         <v>110</v>
       </c>
       <c r="AG2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AJ2" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="AK2" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AL2" t="n">
+        <v>260</v>
+      </c>
+      <c r="AM2" t="n">
         <v>110</v>
       </c>
-      <c r="AM2" t="n">
-        <v>190</v>
-      </c>
       <c r="AN2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AO2" t="n">
         <v>4.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AQ2" t="n">
         <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS2" t="n">
         <v>10.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AU2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
         <v>11.5</v>
@@ -992,7 +992,7 @@
         <v>65</v>
       </c>
       <c r="AY2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AZ2" t="n">
         <v>22</v>
@@ -1001,10 +1001,10 @@
         <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BD2" t="n">
         <v>55</v>
@@ -1013,49 +1013,49 @@
         <v>65</v>
       </c>
       <c r="BF2" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="BG2" t="n">
         <v>3.9</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BJ2" t="n">
         <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BN2" t="n">
         <v>13</v>
       </c>
       <c r="BO2" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BU2" t="n">
         <v>3.75</v>
@@ -1064,13 +1064,13 @@
         <v>7.6</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BX2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G3" t="n">
         <v>1.9</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I3" t="n">
         <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.28</v>
@@ -1141,16 +1141,16 @@
         <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="Q3" t="n">
         <v>1.55</v>
       </c>
       <c r="R3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T3" t="n">
         <v>1.58</v>
@@ -1165,10 +1165,10 @@
         <v>2.1</v>
       </c>
       <c r="X3" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Y3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Z3" t="n">
         <v>40</v>
@@ -1183,7 +1183,7 @@
         <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AE3" t="n">
         <v>55</v>
@@ -1192,22 +1192,22 @@
         <v>14.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ3" t="n">
         <v>23</v>
       </c>
       <c r="AK3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="n">
         <v>200</v>
@@ -1219,46 +1219,46 @@
         <v>48</v>
       </c>
       <c r="AP3" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
         <v>29</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BB3" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD3" t="n">
         <v>20</v>
@@ -1270,7 +1270,7 @@
         <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BH3" t="n">
         <v>4.6</v>
@@ -1282,31 +1282,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
         <v>8.199999999999999</v>
@@ -1318,13 +1318,13 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,239 +1356,239 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thor</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>MAS Maghrib A Fes</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="G4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="AD4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>180</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP4" t="n">
         <v>7.4</v>
       </c>
-      <c r="K4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N4" t="n">
-        <v>18</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X4" t="n">
-        <v>160</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AQ4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>85</v>
+      </c>
+      <c r="BE4" t="n">
         <v>55</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>140</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>330</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>230</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>20</v>
       </c>
       <c r="BF4" t="n">
         <v>10.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.26</v>
+        <v>20</v>
       </c>
       <c r="BH4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN4" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BI4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>14</v>
-      </c>
       <c r="BO4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BP4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BX4" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="BY4" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -1610,49 +1610,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.4</v>
+        <v>1.47</v>
       </c>
       <c r="G5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.52</v>
       </c>
       <c r="H5" t="n">
-        <v>1.62</v>
+        <v>8.6</v>
       </c>
       <c r="I5" t="n">
-        <v>1.66</v>
+        <v>10.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
         <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.27</v>
@@ -1661,188 +1661,188 @@
         <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="U5" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="V5" t="n">
-        <v>2.52</v>
+        <v>1.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>3</v>
       </c>
       <c r="X5" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="Z5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>280</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>14</v>
       </c>
-      <c r="AA5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>400</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>290</v>
-      </c>
       <c r="AK5" t="n">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AM5" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO5" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
         <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>14.5</v>
+        <v>4.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="AZ5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC5" t="n">
         <v>13</v>
       </c>
-      <c r="BA5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>11</v>
-      </c>
       <c r="BD5" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="BE5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BH5" t="n">
         <v>3.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>11</v>
+        <v>3.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.5</v>
+        <v>3.05</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS5" t="n">
         <v>10</v>
       </c>
       <c r="BT5" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.2</v>
+        <v>7.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -1864,239 +1864,239 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DHJ El Jadida</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="G6" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
         <v>4.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="U6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="Z6" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC6" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AD6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK6" t="n">
         <v>23</v>
       </c>
-      <c r="AE6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>24</v>
-      </c>
       <c r="AL6" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>19.5</v>
+        <v>85</v>
       </c>
       <c r="AO6" t="n">
-        <v>280</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>17.5</v>
+        <v>8</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
         <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>10</v>
-      </c>
       <c r="BH6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BO6" t="n">
         <v>3.75</v>
       </c>
       <c r="BP6" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BT6" t="n">
         <v>8.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="BV6" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -2118,239 +2118,239 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I7" t="n">
         <v>4.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="V7" t="n">
         <v>1.27</v>
       </c>
       <c r="W7" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z7" t="n">
         <v>34</v>
       </c>
       <c r="AA7" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE7" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO7" t="n">
         <v>95</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL7" t="n">
+      <c r="AP7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS7" t="n">
         <v>55</v>
       </c>
-      <c r="AM7" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX7" t="n">
         <v>10</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9.6</v>
       </c>
       <c r="AY7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB7" t="n">
         <v>21</v>
       </c>
-      <c r="BA7" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>20</v>
-      </c>
       <c r="BC7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BE7" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BF7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="BJ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
         <v>11.5</v>
       </c>
-      <c r="BK7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BN7" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BP7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW7" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BT7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW7" t="n">
+      <c r="BX7" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY7" t="n">
         <v>10.5</v>
       </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>11</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -2372,109 +2372,109 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>IRT Tanger</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.12</v>
+        <v>1.72</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22</v>
+        <v>1.78</v>
       </c>
       <c r="H8" t="n">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
         <v>1.5</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
         <v>4.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U8" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AA8" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF8" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AL8" t="n">
         <v>55</v>
@@ -2483,128 +2483,128 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AS8" t="n">
         <v>12</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AW8" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>90</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
         <v>10</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>55</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>11</v>
-      </c>
       <c r="BN8" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BR8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS8" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BV8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
         <v>9.6</v>
       </c>
       <c r="BZ8" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="CA8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -2626,239 +2626,239 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="G9" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
         <v>3.85</v>
       </c>
       <c r="L9" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P9" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.25</v>
       </c>
-      <c r="S9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.21</v>
-      </c>
       <c r="W9" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z9" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AF9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="AJ9" t="n">
         <v>24</v>
       </c>
       <c r="AK9" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AL9" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AM9" t="n">
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>600</v>
+        <v>180</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.4</v>
+        <v>4.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>19</v>
-      </c>
       <c r="BA9" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD9" t="n">
         <v>32</v>
       </c>
       <c r="BE9" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BF9" t="n">
         <v>13.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH9" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BO9" t="n">
         <v>3.7</v>
       </c>
       <c r="BP9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW9" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY9" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA9" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Union de Touarga</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IRT Tanger</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.83</v>
+        <v>7.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2</v>
+        <v>1.62</v>
       </c>
       <c r="I10" t="n">
-        <v>5.8</v>
+        <v>1.65</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>2.52</v>
       </c>
       <c r="W10" t="n">
-        <v>2.18</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>290</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>540</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>180</v>
+      </c>
+      <c r="AL10" t="n">
         <v>170</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AM10" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>470</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS10" t="n">
         <v>7</v>
       </c>
-      <c r="AC10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AT10" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>18.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW10" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.6</v>
+        <v>46</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AZ10" t="n">
         <v>21</v>
       </c>
       <c r="BA10" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BB10" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="BD10" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="BE10" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BF10" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>80</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="BJ10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
         <v>8.4</v>
       </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>70</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>95</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>11</v>
-      </c>
       <c r="BZ10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,239 +3134,239 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HUSA Agadir</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.53</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>1.58</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>1.29</v>
       </c>
       <c r="I11" t="n">
-        <v>9.4</v>
+        <v>1.31</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>18</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>6.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.22</v>
+        <v>1.15</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>3.35</v>
       </c>
       <c r="S11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V11" t="n">
         <v>4.2</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.13</v>
-      </c>
       <c r="W11" t="n">
-        <v>2.72</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="Y11" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="Z11" t="n">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="AA11" t="n">
-        <v>430</v>
+        <v>24</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.4</v>
+        <v>180</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="AD11" t="n">
-        <v>36</v>
+        <v>17.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>210</v>
+        <v>14</v>
       </c>
       <c r="AF11" t="n">
-        <v>8</v>
+        <v>180</v>
       </c>
       <c r="AG11" t="n">
-        <v>9.4</v>
+        <v>48</v>
       </c>
       <c r="AH11" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>200</v>
+        <v>19.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>14.5</v>
+        <v>320</v>
       </c>
       <c r="AK11" t="n">
-        <v>21</v>
+        <v>230</v>
       </c>
       <c r="AL11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM11" t="n">
         <v>55</v>
       </c>
-      <c r="AM11" t="n">
-        <v>280</v>
-      </c>
       <c r="AN11" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="AO11" t="n">
-        <v>470</v>
+        <v>2.4</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="AR11" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="AS11" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AT11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>970</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BZ11" t="n">
         <v>4.8</v>
       </c>
-      <c r="AU11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>25</v>
-      </c>
       <c r="CA11" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -3388,239 +3388,239 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MAS Maghrib A Fes</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="G12" t="n">
-        <v>6.4</v>
+        <v>1.88</v>
       </c>
       <c r="H12" t="n">
-        <v>1.83</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>2.92</v>
       </c>
       <c r="O12" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="R12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT12" t="n">
         <v>6.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>700</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>190</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>700</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>890</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>12</v>
       </c>
       <c r="AU12" t="n">
         <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="AX12" t="n">
-        <v>34</v>
+        <v>8.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>23</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BA12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB12" t="n">
-        <v>29</v>
+        <v>17.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="BE12" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="BG12" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -3651,58 +3651,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="G13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H13" t="n">
         <v>2.42</v>
       </c>
-      <c r="H13" t="n">
-        <v>2.62</v>
-      </c>
       <c r="I13" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="R13" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="S13" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="T13" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="U13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="V13" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="W13" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="X13" t="n">
         <v>500</v>
@@ -3723,7 +3723,7 @@
         <v>500</v>
       </c>
       <c r="AD13" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AE13" t="n">
         <v>500</v>
@@ -3732,7 +3732,7 @@
         <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH13" t="n">
         <v>500</v>
@@ -3753,128 +3753,128 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU13" t="n">
         <v>7.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AW13" t="n">
         <v>10.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AZ13" t="n">
         <v>11.5</v>
       </c>
       <c r="BA13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BP13" t="n">
         <v>17</v>
       </c>
-      <c r="BB13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD13" t="n">
+      <c r="BQ13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV13" t="n">
         <v>15.5</v>
       </c>
-      <c r="BE13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF13" t="n">
+      <c r="BW13" t="n">
         <v>5.2</v>
       </c>
-      <c r="BG13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BY13" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BZ13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -3908,22 +3908,22 @@
         <v>1.22</v>
       </c>
       <c r="G14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="H14" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="I14" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="J14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M14" t="n">
         <v>1.01</v>
@@ -3932,34 +3932,34 @@
         <v>11</v>
       </c>
       <c r="O14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q14" t="n">
         <v>1.28</v>
       </c>
       <c r="R14" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="S14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V14" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="X14" t="n">
-        <v>490</v>
+        <v>75</v>
       </c>
       <c r="Y14" t="n">
         <v>1000</v>
@@ -3971,52 +3971,52 @@
         <v>490</v>
       </c>
       <c r="AB14" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD14" t="n">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>12</v>
       </c>
-      <c r="AG14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AK14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL14" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="AM14" t="n">
         <v>490</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AQ14" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AR14" t="n">
         <v>48</v>
@@ -4025,100 +4025,100 @@
         <v>130</v>
       </c>
       <c r="AT14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AW14" t="n">
         <v>48</v>
       </c>
       <c r="AX14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BA14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BB14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC14" t="n">
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BG14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK14" t="n">
         <v>6.4</v>
       </c>
       <c r="BL14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BP14" t="n">
         <v>6.6</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BR14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT14" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BU14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 07:01:44</t>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G15" t="n">
         <v>1.92</v>
       </c>
       <c r="H15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I15" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L15" t="n">
         <v>1.57</v>
@@ -4186,7 +4186,7 @@
         <v>2.78</v>
       </c>
       <c r="O15" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P15" t="n">
         <v>1.57</v>
@@ -4198,13 +4198,13 @@
         <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U15" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V15" t="n">
         <v>1.21</v>
@@ -4213,176 +4213,938 @@
         <v>2.08</v>
       </c>
       <c r="X15" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y15" t="n">
         <v>14</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA15" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AB15" t="n">
         <v>6.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD15" t="n">
         <v>24</v>
       </c>
       <c r="AE15" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF15" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
       </c>
       <c r="AI15" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
         <v>60</v>
       </c>
       <c r="AM15" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AN15" t="n">
         <v>22</v>
       </c>
       <c r="AO15" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AP15" t="n">
         <v>8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR15" t="n">
         <v>34</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW15" t="n">
-        <v>9.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="AX15" t="n">
         <v>8.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BB15" t="n">
         <v>18.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD15" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="BE15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BF15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BG15" t="n">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="BH15" t="n">
         <v>2.86</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BJ15" t="n">
         <v>12.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN15" t="n">
         <v>4.4</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="BP15" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BS15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT15" t="n">
         <v>9</v>
       </c>
       <c r="BU15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>65</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>42</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-07-02 09:14:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Birmingham Legion FC</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Detroit City FC</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X16" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>34</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>23</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>28</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-07-02 09:14:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fortaleza EC</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="X17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>290</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>470</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT17" t="n">
         <v>6.6</v>
       </c>
-      <c r="BV15" t="n">
-        <v>60</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>80</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>40</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>9</v>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>2026-07-02 07:01:44</t>
+      <c r="AU17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>14</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-07-02 09:14:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Boise Cutthroats FC</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>One Knoxville SC</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>950</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-07-02 09:14:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB18"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -848,31 +848,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Asane</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -881,196 +881,196 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Thor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Asane</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1.01</v>
+        <v>300</v>
       </c>
       <c r="H3" t="n">
-        <v>440</v>
+        <v>22</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>120</v>
+        <v>1.05</v>
       </c>
       <c r="K3" t="n">
-        <v>490</v>
+        <v>1.07</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1153,16 +1153,16 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>100</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1210,67 +1210,67 @@
         <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>1.07</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.02</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>250</v>
+        <v>13.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>250</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="BE3" t="n">
-        <v>1000</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG3" t="n">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -1356,239 +1356,239 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MAS Maghrib A Fes</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="H4" t="n">
-        <v>1.96</v>
+        <v>36</v>
       </c>
       <c r="I4" t="n">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.4</v>
+        <v>220</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.7</v>
+        <v>220</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.199999999999999</v>
+        <v>220</v>
       </c>
       <c r="AS4" t="n">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="AT4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BA4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BB4" t="n">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="BC4" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>160</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>13.5</v>
+        <v>1.05</v>
       </c>
       <c r="BG4" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -1610,239 +1610,239 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HUSA Agadir</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.54</v>
+        <v>3.25</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="I5" t="n">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="J5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>220</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>220</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>220</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>220</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4.2</v>
       </c>
-      <c r="K5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="X5" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>950</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>430</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>90</v>
-      </c>
       <c r="BH5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -1864,239 +1864,239 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
-        <v>1.42</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.16</v>
+        <v>1.12</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>1.12</v>
       </c>
       <c r="T6" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>640</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BK6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW6" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BZ6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.06</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>2.14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>1.22</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>1.24</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="S7" t="n">
-        <v>4.6</v>
+        <v>60</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.87</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH7" t="n">
         <v>340</v>
       </c>
-      <c r="AB7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>23</v>
-      </c>
       <c r="AI7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>530</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
         <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>1.13</v>
       </c>
       <c r="AV7" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>50</v>
+        <v>3.35</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>60</v>
+        <v>12.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BD7" t="n">
-        <v>40</v>
+        <v>3.35</v>
       </c>
       <c r="BE7" t="n">
-        <v>75</v>
+        <v>3.35</v>
       </c>
       <c r="BF7" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>55</v>
+        <v>12.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK7" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BQ7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ7" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -2372,239 +2372,239 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Union de Touarga</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IRT Tanger</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="G8" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="H8" t="n">
-        <v>5.7</v>
+        <v>220</v>
       </c>
       <c r="I8" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>95</v>
       </c>
       <c r="K8" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.69</v>
+        <v>1.07</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.32</v>
+        <v>9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="S8" t="n">
-        <v>4.5</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>2.32</v>
+        <v>50</v>
       </c>
       <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
         <v>11</v>
       </c>
-      <c r="Y8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>10</v>
-      </c>
       <c r="AQ8" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="AS8" t="n">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="AU8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY8" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>60</v>
+        <v>7.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>18</v>
+        <v>4.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>42</v>
+        <v>7.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>120</v>
+        <v>4.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>100</v>
+        <v>7.8</v>
       </c>
       <c r="BH8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BQ8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BZ8" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -2626,239 +2626,239 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Union de Touarga</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DHJ El Jadida</t>
+          <t>IRT Tanger</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="G9" t="n">
-        <v>1.96</v>
+        <v>1.04</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>17.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>200</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>50</v>
       </c>
       <c r="R9" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="S9" t="n">
-        <v>4.1</v>
+        <v>1.75</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="U9" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>2.06</v>
+        <v>25</v>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>8</v>
+        <v>1.17</v>
       </c>
       <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY9" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>19</v>
+        <v>7.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>50</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>19.5</v>
+        <v>8.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>36</v>
+        <v>5.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>14.5</v>
+        <v>1.06</v>
       </c>
       <c r="BG9" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BQ9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>HUSA Agadir</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9.800000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="G10" t="n">
-        <v>10.5</v>
+        <v>1.15</v>
       </c>
       <c r="H10" t="n">
-        <v>1.48</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>1.51</v>
+        <v>390</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>9.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.55</v>
+        <v>1.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.36</v>
+        <v>3.9</v>
       </c>
       <c r="P10" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>44</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="S10" t="n">
-        <v>3.85</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>8</v>
       </c>
       <c r="X10" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>26</v>
+        <v>1.27</v>
       </c>
       <c r="AC10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>490</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>430</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AS10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AT10" t="n">
-        <v>22</v>
+        <v>1.14</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="AW10" t="n">
-        <v>15.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>60</v>
+        <v>5.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>30</v>
+        <v>6.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="BA10" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="BB10" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="BD10" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="BE10" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="BF10" t="n">
-        <v>180</v>
+        <v>6.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BO10" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ10" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thor</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>MAS Maghrib A Fes</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="G11" t="n">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="H11" t="n">
-        <v>1.31</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>1.33</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>7.4</v>
+        <v>1.15</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>1.19</v>
       </c>
       <c r="L11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="N11" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
-        <v>1.04</v>
+        <v>46</v>
       </c>
       <c r="P11" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="Q11" t="n">
+        <v>100</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>290</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
         <v>1.15</v>
       </c>
-      <c r="R11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X11" t="n">
-        <v>140</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>200</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>450</v>
-      </c>
-      <c r="AG11" t="n">
+      <c r="AQ11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>46</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BF11" t="n">
         <v>44</v>
       </c>
-      <c r="AH11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>350</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>230</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>80</v>
-      </c>
-      <c r="BD11" t="n">
+      <c r="BG11" t="n">
         <v>44</v>
       </c>
-      <c r="BE11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>26</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.18</v>
-      </c>
       <c r="BH11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BK11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BN11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BO11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BZ11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>Ymir</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>KV Vesturbaejar</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.83</v>
+        <v>2.22</v>
       </c>
       <c r="G12" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="H12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X12" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>120</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>8</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>55</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="CA12" t="n">
         <v>5.2</v>
       </c>
-      <c r="I12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="X12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>75</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>34</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>10</v>
-      </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,246 +3642,246 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ymir</t>
+          <t>Vikingur Reykjavik</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KV Vesturbaejar</t>
+          <t>KA Akureyri</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.46</v>
+        <v>1.2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.58</v>
+        <v>1.21</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4</v>
+        <v>15.5</v>
       </c>
       <c r="I13" t="n">
+        <v>16</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>12</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>230</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>210</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN13" t="n">
         <v>2.56</v>
       </c>
-      <c r="J13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="P13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X13" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AO13" t="n">
-        <v>6.6</v>
+        <v>190</v>
       </c>
       <c r="AP13" t="n">
         <v>60</v>
       </c>
       <c r="AQ13" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.2</v>
+        <v>70</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.4</v>
+        <v>130</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="AU13" t="n">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="AV13" t="n">
-        <v>14.5</v>
+        <v>48</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
+        <v>29</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>80</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BJ13" t="n">
         <v>12</v>
       </c>
-      <c r="BA13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BK13" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BL13" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM13" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="BN13" t="n">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="BP13" t="n">
-        <v>17</v>
+        <v>6.2</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BR13" t="n">
         <v>16.5</v>
       </c>
       <c r="BS13" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BV13" t="n">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX13" t="n">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="BY13" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,244 +3891,244 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Vikingur Reykjavik</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KA Akureyri</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.2</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="H14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="S14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA14" t="n">
         <v>16.5</v>
       </c>
-      <c r="J14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="BB14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>240</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW14" t="n">
         <v>9.6</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="X14" t="n">
-        <v>70</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="BX14" t="n">
         <v>80</v>
       </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>600</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>490</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>48</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>130</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BG14" t="n">
+      <c r="BY14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ14" t="n">
         <v>42</v>
       </c>
-      <c r="BH14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>85</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>75</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>16</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>17</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>0</v>
-      </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -4145,244 +4145,244 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.89</v>
+        <v>1.31</v>
       </c>
       <c r="G15" t="n">
-        <v>1.92</v>
+        <v>1.33</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>14</v>
       </c>
       <c r="J15" t="n">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.78</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>1.59</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.62</v>
+        <v>1.82</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="T15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="V15" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="W15" t="n">
-        <v>2.08</v>
+        <v>4</v>
       </c>
       <c r="X15" t="n">
-        <v>9.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="Y15" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>620</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC15" t="n">
         <v>13</v>
       </c>
-      <c r="Z15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AD15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX15" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR15" t="n">
+      <c r="AY15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>32</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>25</v>
       </c>
       <c r="BA15" t="n">
         <v>16</v>
       </c>
       <c r="BB15" t="n">
-        <v>18.5</v>
+        <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="BD15" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BE15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG15" t="n">
         <v>17</v>
       </c>
-      <c r="BF15" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG15" t="n">
+      <c r="BH15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>210</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>130</v>
+      </c>
+      <c r="BW15" t="n">
         <v>15</v>
       </c>
-      <c r="BH15" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>240</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>16</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>60</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BX15" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="BY15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>14</v>
+      </c>
+      <c r="CA15" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BZ15" t="n">
-        <v>42</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G16" t="n">
         <v>2.94</v>
@@ -4422,7 +4422,7 @@
         <v>2.6</v>
       </c>
       <c r="I16" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J16" t="n">
         <v>3.55</v>
@@ -4443,7 +4443,7 @@
         <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
         <v>2</v>
@@ -4455,10 +4455,10 @@
         <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U16" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V16" t="n">
         <v>1.6</v>
@@ -4470,10 +4470,10 @@
         <v>14</v>
       </c>
       <c r="Y16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AA16" t="n">
         <v>44</v>
@@ -4482,7 +4482,7 @@
         <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
         <v>14</v>
@@ -4491,7 +4491,7 @@
         <v>38</v>
       </c>
       <c r="AF16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG16" t="n">
         <v>15</v>
@@ -4500,22 +4500,22 @@
         <v>22</v>
       </c>
       <c r="AI16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN16" t="n">
         <v>34</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>30</v>
       </c>
       <c r="AO16" t="n">
         <v>28</v>
@@ -4527,10 +4527,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.2</v>
+        <v>27</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -4542,7 +4542,7 @@
         <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX16" t="n">
         <v>16.5</v>
@@ -4551,40 +4551,40 @@
         <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.2</v>
+        <v>34</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.2</v>
+        <v>30</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.1</v>
+        <v>24</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.3</v>
+        <v>32</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.4</v>
+        <v>70</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.3</v>
+        <v>21</v>
       </c>
       <c r="BG16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK16" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4602,13 +4602,13 @@
         <v>24</v>
       </c>
       <c r="BQ16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BR16" t="n">
         <v>36</v>
       </c>
       <c r="BS16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BT16" t="n">
         <v>5.8</v>
@@ -4629,21 +4629,21 @@
         <v>23</v>
       </c>
       <c r="BZ16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,498 +4653,244 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Boise Cutthroats FC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>One Knoxville SC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.32</v>
+        <v>2.34</v>
       </c>
       <c r="G17" t="n">
-        <v>1.35</v>
+        <v>2.6</v>
       </c>
       <c r="H17" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="I17" t="n">
-        <v>13.5</v>
+        <v>3.35</v>
       </c>
       <c r="J17" t="n">
-        <v>5.6</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.36</v>
       </c>
-      <c r="M17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.43</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.08</v>
-      </c>
       <c r="W17" t="n">
-        <v>3.85</v>
+        <v>1.63</v>
       </c>
       <c r="X17" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-02 13:44:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Boise Cutthroats FC</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>One Knoxville SC</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB18" t="inlineStr">
-        <is>
-          <t>2026-07-02 13:44:29</t>
+          <t>2026-07-02 15:58:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.99</v>
+        <v>1.1</v>
       </c>
       <c r="G2" t="n">
-        <v>2.04</v>
+        <v>1.12</v>
       </c>
       <c r="H2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" t="n">
+        <v>150</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="S2" t="n">
+        <v>30</v>
+      </c>
+      <c r="T2" t="n">
         <v>5.7</v>
       </c>
-      <c r="I2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>10</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.96</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.97</v>
+        <v>9.4</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>180</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>280</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB2" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="BC2" t="n">
         <v>55</v>
       </c>
-      <c r="AA2" t="n">
-        <v>260</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>510</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>140</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>170</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC2" t="n">
+      <c r="BD2" t="n">
+        <v>80</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF2" t="n">
         <v>32</v>
       </c>
-      <c r="BD2" t="n">
-        <v>100</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>230</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>36</v>
-      </c>
       <c r="BG2" t="n">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="BH2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,246 +1102,246 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Birmingham Legion FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.31</v>
+        <v>5.4</v>
       </c>
       <c r="G3" t="n">
-        <v>1.32</v>
+        <v>6.2</v>
       </c>
       <c r="H3" t="n">
-        <v>13.5</v>
+        <v>3.1</v>
       </c>
       <c r="I3" t="n">
-        <v>14</v>
+        <v>3.45</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9</v>
+        <v>1.83</v>
       </c>
       <c r="K3" t="n">
-        <v>6.2</v>
+        <v>1.97</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>3.05</v>
+        <v>5.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>4.1</v>
+        <v>1.19</v>
       </c>
       <c r="X3" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>630</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.5</v>
+        <v>2.26</v>
       </c>
       <c r="AD3" t="n">
-        <v>50</v>
+        <v>4.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>280</v>
+        <v>24</v>
       </c>
       <c r="AF3" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>38</v>
+        <v>14.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>530</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AK3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>440</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU3" t="n">
+      <c r="AX3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>12.5</v>
       </c>
-      <c r="AV3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>32</v>
-      </c>
       <c r="BA3" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="BB3" t="n">
         <v>8.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="BD3" t="n">
-        <v>40</v>
+        <v>14.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>130</v>
+        <v>12</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,498 +1351,244 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Birmingham Legion FC</t>
+          <t>Boise Cutthroats FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>One Knoxville SC</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.7</v>
+        <v>1.92</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78</v>
+        <v>2.26</v>
       </c>
       <c r="H4" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>3.55</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="W4" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="X4" t="n">
+        <v>220</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
         <v>14</v>
       </c>
-      <c r="Y4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AD4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AO4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>1.14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>17</v>
+        <v>1.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>40</v>
+        <v>1.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.800000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>1.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>11.5</v>
+        <v>1.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>28</v>
+        <v>1.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>15.5</v>
+        <v>1.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>1.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16</v>
+        <v>1.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>38</v>
+        <v>1.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>38</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>26</v>
+        <v>1.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>36</v>
+        <v>1.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>75</v>
+        <v>1.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>21</v>
+        <v>1.12</v>
       </c>
       <c r="BG4" t="n">
-        <v>24</v>
+        <v>1.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.45</v>
+        <v>710</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>28</v>
+        <v>960</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-02 20:27:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>US USL League One</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Boise Cutthroats FC</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>One Knoxville SC</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="X5" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-07-02 20:27:49</t>
+          <t>2026-07-02 22:42:30</t>
         </is>
       </c>
     </row>
